--- a/tests/data/test_foods.xlsx
+++ b/tests/data/test_foods.xlsx
@@ -437,6 +437,11 @@
           <t>KCAL</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>WATER</t>
+        </is>
+      </c>
       <c r="M1" t="inlineStr">
         <is>
           <t>PROTEIN</t>
@@ -520,52 +525,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.73937720733721</v>
+        <v>2949.193369233891</v>
       </c>
       <c r="G2" t="n">
-        <v>314.3546975814773</v>
+        <v>88.03986107887498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.540503426697308</v>
       </c>
       <c r="M2" t="n">
-        <v>11.02101249685558</v>
+        <v>68.60967124556362</v>
       </c>
       <c r="P2" t="n">
-        <v>2.503792987346865</v>
+        <v>5.500013190911712</v>
       </c>
       <c r="S2" t="n">
-        <v>39.76391994126348</v>
+        <v>25.8861951438792</v>
       </c>
       <c r="V2" t="n">
-        <v>40.80644641652958</v>
+        <v>1.580202540496933</v>
       </c>
       <c r="AH2" t="n">
-        <v>342.8884299273245</v>
+        <v>120.7810008967047</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.53520892349645</v>
+        <v>11.41377622535997</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.349700642542746</v>
+        <v>6.052228130487047</v>
       </c>
       <c r="DO2" t="n">
-        <v>23.16559641239002</v>
+        <v>71.2896472020993</v>
       </c>
       <c r="EC2" t="n">
-        <v>703.9858936630993</v>
+        <v>81.75616535348162</v>
       </c>
       <c r="EF2" t="n">
-        <v>263.2046901553801</v>
+        <v>153.6795801129233</v>
       </c>
       <c r="EO2" t="n">
-        <v>12.04638540085693</v>
+        <v>14.59415964868128</v>
       </c>
       <c r="ER2" t="n">
-        <v>14.60444264009874</v>
+        <v>10.25473697279223</v>
       </c>
       <c r="HL2" t="n">
-        <v>1.320827727889784</v>
+        <v>4.810442570642259</v>
       </c>
       <c r="LA2" t="n">
-        <v>1.776144739248707</v>
+        <v>3.301727158366965</v>
       </c>
     </row>
     <row r="3">
@@ -580,52 +588,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1682.96410481071</v>
+        <v>389.6445878680908</v>
       </c>
       <c r="G3" t="n">
-        <v>679.7116491575028</v>
+        <v>240.6632795037005</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45.38514540130074</v>
       </c>
       <c r="M3" t="n">
-        <v>80.87162391360569</v>
+        <v>56.3938056013524</v>
       </c>
       <c r="P3" t="n">
-        <v>12.21756019722359</v>
+        <v>60.94651550853717</v>
       </c>
       <c r="S3" t="n">
-        <v>72.16881248537145</v>
+        <v>60.1650645913562</v>
       </c>
       <c r="V3" t="n">
-        <v>35.13747212301478</v>
+        <v>19.59038604779204</v>
       </c>
       <c r="AH3" t="n">
-        <v>878.6497420711362</v>
+        <v>974.3400668111948</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.468373415626913</v>
+        <v>2.892712813164631</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.586231925984007</v>
+        <v>0.3525288850023223</v>
       </c>
       <c r="DO3" t="n">
-        <v>36.99698705982796</v>
+        <v>46.03968760828927</v>
       </c>
       <c r="EC3" t="n">
-        <v>227.9996962132993</v>
+        <v>780.4416514463564</v>
       </c>
       <c r="EF3" t="n">
-        <v>169.4073968122135</v>
+        <v>414.5506859248928</v>
       </c>
       <c r="EO3" t="n">
-        <v>17.27253747044297</v>
+        <v>13.89758352287901</v>
       </c>
       <c r="ER3" t="n">
-        <v>16.53088695522147</v>
+        <v>11.25919485752307</v>
       </c>
       <c r="HL3" t="n">
-        <v>94.79099739654129</v>
+        <v>83.04120824420453</v>
       </c>
       <c r="LA3" t="n">
-        <v>3.473068149653869</v>
+        <v>0.6498995307466782</v>
       </c>
     </row>
     <row r="4">
@@ -640,52 +651,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1392.283828473224</v>
+        <v>2547.096443180427</v>
       </c>
       <c r="G4" t="n">
-        <v>596.6289482344318</v>
+        <v>347.5151928089571</v>
+      </c>
+      <c r="J4" t="n">
+        <v>90.40806705978876</v>
       </c>
       <c r="M4" t="n">
-        <v>50.76059789459728</v>
+        <v>10.06296266730248</v>
       </c>
       <c r="P4" t="n">
-        <v>26.04317078069759</v>
+        <v>13.16995929873703</v>
       </c>
       <c r="S4" t="n">
-        <v>74.44138558584218</v>
+        <v>8.108341753269087</v>
       </c>
       <c r="V4" t="n">
-        <v>18.24939776561472</v>
+        <v>45.93744634405403</v>
       </c>
       <c r="AH4" t="n">
-        <v>213.2239584892073</v>
+        <v>319.5538389955844</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.8790622813127</v>
+        <v>4.641020426074767</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.40605501988199</v>
+        <v>0.2103805082856391</v>
       </c>
       <c r="DO4" t="n">
-        <v>89.11993383802447</v>
+        <v>85.68443253708729</v>
       </c>
       <c r="EC4" t="n">
-        <v>247.0899131204351</v>
+        <v>313.6203810113041</v>
       </c>
       <c r="EF4" t="n">
-        <v>90.87241485110964</v>
+        <v>330.5603048253438</v>
       </c>
       <c r="EO4" t="n">
-        <v>12.14910735713309</v>
+        <v>15.42854187020017</v>
       </c>
       <c r="ER4" t="n">
-        <v>19.28235098100872</v>
+        <v>13.81735280120892</v>
       </c>
       <c r="HL4" t="n">
-        <v>62.37694183880844</v>
+        <v>21.58529150132625</v>
       </c>
       <c r="LA4" t="n">
-        <v>4.798204766972943</v>
+        <v>3.759038033655725</v>
       </c>
     </row>
     <row r="5">
@@ -700,52 +714,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1258.419616029428</v>
+        <v>1311.4423169146</v>
       </c>
       <c r="G5" t="n">
-        <v>588.1140655672505</v>
+        <v>687.8511268295164</v>
+      </c>
+      <c r="J5" t="n">
+        <v>74.07220161347271</v>
       </c>
       <c r="M5" t="n">
-        <v>99.83803044200032</v>
+        <v>27.50833046294382</v>
       </c>
       <c r="P5" t="n">
-        <v>74.36286160424339</v>
+        <v>81.69048141850072</v>
       </c>
       <c r="S5" t="n">
-        <v>4.196364531077156</v>
+        <v>60.96038501978332</v>
       </c>
       <c r="V5" t="n">
-        <v>46.48574877869018</v>
+        <v>4.62053783780661</v>
       </c>
       <c r="AH5" t="n">
-        <v>983.116889323366</v>
+        <v>707.5332182918052</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.718874960681758</v>
+        <v>17.99587914315335</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.573896059339405</v>
+        <v>4.852115048743038</v>
       </c>
       <c r="DO5" t="n">
-        <v>9.888815756564517</v>
+        <v>33.85863543114079</v>
       </c>
       <c r="EC5" t="n">
-        <v>793.471892736447</v>
+        <v>821.9418734426237</v>
       </c>
       <c r="EF5" t="n">
-        <v>291.7572486607702</v>
+        <v>214.7604083463299</v>
       </c>
       <c r="EO5" t="n">
-        <v>6.071304975202716</v>
+        <v>11.99864226338151</v>
       </c>
       <c r="ER5" t="n">
-        <v>5.14428153506632</v>
+        <v>9.096902742465808</v>
       </c>
       <c r="HL5" t="n">
-        <v>33.15633393342659</v>
+        <v>97.04547058303091</v>
       </c>
       <c r="LA5" t="n">
-        <v>1.771921994363659</v>
+        <v>2.827383886753538</v>
       </c>
     </row>
     <row r="6">
@@ -760,52 +777,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>361.1975338732154</v>
+        <v>2302.503414419364</v>
       </c>
       <c r="G6" t="n">
-        <v>606.2976941679557</v>
+        <v>734.8433744419169</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.822962477416372</v>
       </c>
       <c r="M6" t="n">
-        <v>46.96168197308549</v>
+        <v>15.35882236454539</v>
       </c>
       <c r="P6" t="n">
-        <v>20.23687250904822</v>
+        <v>37.45805075626498</v>
       </c>
       <c r="S6" t="n">
-        <v>84.38173241411474</v>
+        <v>24.78152343326045</v>
       </c>
       <c r="V6" t="n">
-        <v>30.75459543583176</v>
+        <v>1.337754990997081</v>
       </c>
       <c r="AH6" t="n">
-        <v>615.7573006826127</v>
+        <v>634.5587035706388</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.63136631851545</v>
+        <v>2.44336588200422</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.1668400511631452</v>
+        <v>0.02443063420028313</v>
       </c>
       <c r="DO6" t="n">
-        <v>28.74894928518854</v>
+        <v>66.05070851145616</v>
       </c>
       <c r="EC6" t="n">
-        <v>832.2311909123904</v>
+        <v>45.58244537853573</v>
       </c>
       <c r="EF6" t="n">
-        <v>39.60406184471471</v>
+        <v>322.2098526657074</v>
       </c>
       <c r="EO6" t="n">
-        <v>11.96967796405163</v>
+        <v>13.53286587778642</v>
       </c>
       <c r="ER6" t="n">
-        <v>15.65654987542053</v>
+        <v>8.756754932737799</v>
       </c>
       <c r="HL6" t="n">
-        <v>7.923669592635518</v>
+        <v>27.70788441512786</v>
       </c>
       <c r="LA6" t="n">
-        <v>1.753987919022617</v>
+        <v>0.2743480875894355</v>
       </c>
     </row>
     <row r="7">
@@ -820,52 +840,55 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2310.393611008871</v>
+        <v>1948.00657945921</v>
       </c>
       <c r="G7" t="n">
-        <v>602.2183190947404</v>
+        <v>773.1488629838229</v>
+      </c>
+      <c r="J7" t="n">
+        <v>49.30460684720981</v>
       </c>
       <c r="M7" t="n">
-        <v>12.10740217978659</v>
+        <v>46.09759265879036</v>
       </c>
       <c r="P7" t="n">
-        <v>50.40413016688906</v>
+        <v>27.28494923848157</v>
       </c>
       <c r="S7" t="n">
-        <v>17.43931007623572</v>
+        <v>70.72927808887985</v>
       </c>
       <c r="V7" t="n">
-        <v>9.932426112520959</v>
+        <v>26.93465162113432</v>
       </c>
       <c r="AH7" t="n">
-        <v>492.1899735947815</v>
+        <v>607.3524603222536</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.82745059126713</v>
+        <v>4.329086777428519</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.1714157573494</v>
+        <v>1.900394861091848</v>
       </c>
       <c r="DO7" t="n">
-        <v>69.22004435099456</v>
+        <v>80.15687794066052</v>
       </c>
       <c r="EC7" t="n">
-        <v>740.958265448159</v>
+        <v>711.8259876419585</v>
       </c>
       <c r="EF7" t="n">
-        <v>325.9030925685605</v>
+        <v>282.2506847692177</v>
       </c>
       <c r="EO7" t="n">
-        <v>14.9537749076046</v>
+        <v>12.75964654060497</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.2914131187779923</v>
+        <v>2.84210558818877</v>
       </c>
       <c r="HL7" t="n">
-        <v>20.09153892383602</v>
+        <v>2.06069933307379</v>
       </c>
       <c r="LA7" t="n">
-        <v>4.610457319398651</v>
+        <v>4.340262066941322</v>
       </c>
     </row>
     <row r="8">
@@ -880,52 +903,55 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>992.9169939243167</v>
+        <v>2550.226009975374</v>
       </c>
       <c r="G8" t="n">
-        <v>620.617329806978</v>
+        <v>294.481217762745</v>
+      </c>
+      <c r="J8" t="n">
+        <v>73.6625527133023</v>
       </c>
       <c r="M8" t="n">
-        <v>16.45826893188783</v>
+        <v>84.71726413577538</v>
       </c>
       <c r="P8" t="n">
-        <v>86.60760834801445</v>
+        <v>32.22164669483397</v>
       </c>
       <c r="S8" t="n">
-        <v>99.4581823385484</v>
+        <v>85.88460144523198</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7714311394061257</v>
+        <v>7.790634847298278</v>
       </c>
       <c r="AH8" t="n">
-        <v>168.7813782962834</v>
+        <v>701.99073086628</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.953888600399567</v>
+        <v>11.96343125992886</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.755143744469295</v>
+        <v>4.860481622230198</v>
       </c>
       <c r="DO8" t="n">
-        <v>42.97493421140205</v>
+        <v>37.86157377737895</v>
       </c>
       <c r="EC8" t="n">
-        <v>607.0166299382237</v>
+        <v>43.12336420345731</v>
       </c>
       <c r="EF8" t="n">
-        <v>92.85611604683081</v>
+        <v>297.3676709349463</v>
       </c>
       <c r="EO8" t="n">
-        <v>5.437570362739024</v>
+        <v>2.487014870732243</v>
       </c>
       <c r="ER8" t="n">
-        <v>14.70008352281113</v>
+        <v>4.285061468442981</v>
       </c>
       <c r="HL8" t="n">
-        <v>87.3812637734793</v>
+        <v>0.1012806213670614</v>
       </c>
       <c r="LA8" t="n">
-        <v>4.944444689865711</v>
+        <v>3.688864607983323</v>
       </c>
     </row>
     <row r="9">
@@ -940,52 +966,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2284.317204023454</v>
+        <v>1007.022729403996</v>
       </c>
       <c r="G9" t="n">
-        <v>757.5119057974273</v>
+        <v>761.5384238950314</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57.51894632742344</v>
       </c>
       <c r="M9" t="n">
-        <v>2.997811596298339</v>
+        <v>85.76553503955407</v>
       </c>
       <c r="P9" t="n">
-        <v>96.83019630061689</v>
+        <v>9.870043071542089</v>
       </c>
       <c r="S9" t="n">
-        <v>61.72555676199116</v>
+        <v>52.76187537317362</v>
       </c>
       <c r="V9" t="n">
-        <v>23.95907342790999</v>
+        <v>9.926503811762139</v>
       </c>
       <c r="AH9" t="n">
-        <v>993.1392136755494</v>
+        <v>327.7695233847517</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.51724186926255</v>
+        <v>6.018321490850247</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.579040088636529</v>
+        <v>3.461479692791315</v>
       </c>
       <c r="DO9" t="n">
-        <v>63.650027157061</v>
+        <v>10.94331701430109</v>
       </c>
       <c r="EC9" t="n">
-        <v>998.1300756178462</v>
+        <v>734.6445471726978</v>
       </c>
       <c r="EF9" t="n">
-        <v>329.2567153063584</v>
+        <v>336.2407063680999</v>
       </c>
       <c r="EO9" t="n">
-        <v>1.244664089915717</v>
+        <v>16.19277134504773</v>
       </c>
       <c r="ER9" t="n">
-        <v>5.070311430920025</v>
+        <v>14.19101664226736</v>
       </c>
       <c r="HL9" t="n">
-        <v>98.32784067615576</v>
+        <v>56.18026857742115</v>
       </c>
       <c r="LA9" t="n">
-        <v>4.371528124665051</v>
+        <v>4.325982671542953</v>
       </c>
     </row>
     <row r="10">
@@ -1000,52 +1029,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>317.8323613843909</v>
+        <v>838.8760099642859</v>
       </c>
       <c r="G10" t="n">
-        <v>440.8326371941308</v>
+        <v>189.2041329099387</v>
+      </c>
+      <c r="J10" t="n">
+        <v>68.62495446402664</v>
       </c>
       <c r="M10" t="n">
-        <v>58.65965291265189</v>
+        <v>9.623220684838396</v>
       </c>
       <c r="P10" t="n">
-        <v>95.85825080205026</v>
+        <v>23.83224263592058</v>
       </c>
       <c r="S10" t="n">
-        <v>38.48618467280539</v>
+        <v>53.03140671759328</v>
       </c>
       <c r="V10" t="n">
-        <v>14.21693435972439</v>
+        <v>33.10059801593855</v>
       </c>
       <c r="AH10" t="n">
-        <v>307.6040046152884</v>
+        <v>566.1659438881236</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.9190461590016574</v>
+        <v>8.629531484043692</v>
       </c>
       <c r="DK10" t="n">
-        <v>6.720536223785971</v>
+        <v>5.040620823571143</v>
       </c>
       <c r="DO10" t="n">
-        <v>43.70728392544317</v>
+        <v>66.96131528440462</v>
       </c>
       <c r="EC10" t="n">
-        <v>793.5768360459672</v>
+        <v>62.97675597267416</v>
       </c>
       <c r="EF10" t="n">
-        <v>92.86357979983023</v>
+        <v>167.8950426824551</v>
       </c>
       <c r="EO10" t="n">
-        <v>17.49970924925932</v>
+        <v>6.431119693909981</v>
       </c>
       <c r="ER10" t="n">
-        <v>9.802776183526067</v>
+        <v>6.461210939378002</v>
       </c>
       <c r="HL10" t="n">
-        <v>82.84494892320123</v>
+        <v>23.14841572517065</v>
       </c>
       <c r="LA10" t="n">
-        <v>3.377682718000679</v>
+        <v>0.646692671034666</v>
       </c>
     </row>
     <row r="11">
@@ -1060,52 +1092,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2063.270442978338</v>
+        <v>1976.113629085567</v>
       </c>
       <c r="G11" t="n">
-        <v>168.0062241093413</v>
+        <v>7.791141745370567</v>
+      </c>
+      <c r="J11" t="n">
+        <v>70.08171554626966</v>
       </c>
       <c r="M11" t="n">
-        <v>75.16407673677938</v>
+        <v>77.91949621059607</v>
       </c>
       <c r="P11" t="n">
-        <v>73.43650803361299</v>
+        <v>50.50050473216855</v>
       </c>
       <c r="S11" t="n">
-        <v>33.14423178155293</v>
+        <v>36.38309941385452</v>
       </c>
       <c r="V11" t="n">
-        <v>31.14908981366835</v>
+        <v>29.03325860229132</v>
       </c>
       <c r="AH11" t="n">
-        <v>30.50278038563836</v>
+        <v>634.7008131916799</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.207114376406878</v>
+        <v>15.21883043298971</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.671578957646259</v>
+        <v>9.39684459404778</v>
       </c>
       <c r="DO11" t="n">
-        <v>46.24338798177524</v>
+        <v>89.34006824874093</v>
       </c>
       <c r="EC11" t="n">
-        <v>937.8103935713026</v>
+        <v>17.41942064240365</v>
       </c>
       <c r="EF11" t="n">
-        <v>424.6217221046325</v>
+        <v>234.5096541713358</v>
       </c>
       <c r="EO11" t="n">
-        <v>14.0404457922422</v>
+        <v>1.204717206725272</v>
       </c>
       <c r="ER11" t="n">
-        <v>6.676415640914892</v>
+        <v>15.83357149386845</v>
       </c>
       <c r="HL11" t="n">
-        <v>83.72531200126726</v>
+        <v>20.96465564051941</v>
       </c>
       <c r="LA11" t="n">
-        <v>3.229504842390133</v>
+        <v>3.826452979342211</v>
       </c>
     </row>
     <row r="12">
@@ -1120,52 +1155,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>656.7461199422842</v>
+        <v>1508.617961586515</v>
       </c>
       <c r="G12" t="n">
-        <v>646.7821666883706</v>
+        <v>590.3354696967461</v>
+      </c>
+      <c r="J12" t="n">
+        <v>76.13159349564091</v>
       </c>
       <c r="M12" t="n">
-        <v>12.43960825250281</v>
+        <v>3.731056922091147</v>
       </c>
       <c r="P12" t="n">
-        <v>40.96797723354688</v>
+        <v>26.39605701424804</v>
       </c>
       <c r="S12" t="n">
-        <v>54.62571733779189</v>
+        <v>51.48716066028241</v>
       </c>
       <c r="V12" t="n">
-        <v>17.3256945470177</v>
+        <v>15.95193024629168</v>
       </c>
       <c r="AH12" t="n">
-        <v>175.2646701643161</v>
+        <v>551.191209985496</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.24260766168638</v>
+        <v>1.526954998298407</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.818647359413939</v>
+        <v>4.041643516626277</v>
       </c>
       <c r="DO12" t="n">
-        <v>86.10490261259517</v>
+        <v>37.87052606109571</v>
       </c>
       <c r="EC12" t="n">
-        <v>682.7046533845567</v>
+        <v>78.95871600872528</v>
       </c>
       <c r="EF12" t="n">
-        <v>121.6963969414222</v>
+        <v>393.9149821959685</v>
       </c>
       <c r="EO12" t="n">
-        <v>13.099114881141</v>
+        <v>13.14158770839672</v>
       </c>
       <c r="ER12" t="n">
-        <v>11.18798510059895</v>
+        <v>6.493913055633587</v>
       </c>
       <c r="HL12" t="n">
-        <v>49.46580176208909</v>
+        <v>88.21000008000527</v>
       </c>
       <c r="LA12" t="n">
-        <v>2.765955786874766</v>
+        <v>4.453010045319753</v>
       </c>
     </row>
     <row r="13">
@@ -1180,52 +1218,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2898.273394297763</v>
+        <v>210.7679369133314</v>
       </c>
       <c r="G13" t="n">
-        <v>120.4654245144165</v>
+        <v>189.3019935074615</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38.07124363602284</v>
       </c>
       <c r="M13" t="n">
-        <v>57.31963336083113</v>
+        <v>25.88155779460397</v>
       </c>
       <c r="P13" t="n">
-        <v>72.23352540301312</v>
+        <v>24.49742962853193</v>
       </c>
       <c r="S13" t="n">
-        <v>23.84957688072077</v>
+        <v>25.62935865091164</v>
       </c>
       <c r="V13" t="n">
-        <v>34.90495661700166</v>
+        <v>36.19471785817162</v>
       </c>
       <c r="AH13" t="n">
-        <v>349.910834818101</v>
+        <v>924.1035633065827</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.778678155210451</v>
+        <v>2.512408850576369</v>
       </c>
       <c r="DK13" t="n">
-        <v>6.533567662334875</v>
+        <v>1.761618580883483</v>
       </c>
       <c r="DO13" t="n">
-        <v>10.40120699502626</v>
+        <v>44.24140108152977</v>
       </c>
       <c r="EC13" t="n">
-        <v>274.8359391987857</v>
+        <v>210.2941858056497</v>
       </c>
       <c r="EF13" t="n">
-        <v>476.8314991751599</v>
+        <v>99.97952292709122</v>
       </c>
       <c r="EO13" t="n">
-        <v>6.130749770298847</v>
+        <v>9.61909502566038</v>
       </c>
       <c r="ER13" t="n">
-        <v>9.373020062872774</v>
+        <v>7.490195320087372</v>
       </c>
       <c r="HL13" t="n">
-        <v>0.05490716762074355</v>
+        <v>69.02190008858838</v>
       </c>
       <c r="LA13" t="n">
-        <v>1.12088676228105</v>
+        <v>1.285360251692522</v>
       </c>
     </row>
     <row r="14">
@@ -1240,52 +1281,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2860.807968677374</v>
+        <v>579.3447708699752</v>
       </c>
       <c r="G14" t="n">
-        <v>599.1581878579867</v>
+        <v>129.7804297074081</v>
+      </c>
+      <c r="J14" t="n">
+        <v>44.64562042714433</v>
       </c>
       <c r="M14" t="n">
-        <v>44.89268223773358</v>
+        <v>93.1007361041036</v>
       </c>
       <c r="P14" t="n">
-        <v>68.36810333143362</v>
+        <v>39.22525688835079</v>
       </c>
       <c r="S14" t="n">
-        <v>30.3878243944097</v>
+        <v>50.34194192781185</v>
       </c>
       <c r="V14" t="n">
-        <v>15.35647916701581</v>
+        <v>45.32985531763731</v>
       </c>
       <c r="AH14" t="n">
-        <v>930.5541641209675</v>
+        <v>348.2472738442414</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.03959307254178</v>
+        <v>12.87180483767257</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.018062770863125</v>
+        <v>3.831219400971619</v>
       </c>
       <c r="DO14" t="n">
-        <v>34.46169446386054</v>
+        <v>69.44681683628116</v>
       </c>
       <c r="EC14" t="n">
-        <v>68.92995533918645</v>
+        <v>530.329349016291</v>
       </c>
       <c r="EF14" t="n">
-        <v>162.11899985188</v>
+        <v>35.98170061483025</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.8298597893282822</v>
+        <v>3.344852533508156</v>
       </c>
       <c r="ER14" t="n">
-        <v>11.27806193205999</v>
+        <v>2.999622750538822</v>
       </c>
       <c r="HL14" t="n">
-        <v>78.30433339261478</v>
+        <v>98.42092971443596</v>
       </c>
       <c r="LA14" t="n">
-        <v>3.553092548511378</v>
+        <v>1.820732655704478</v>
       </c>
     </row>
     <row r="15">
@@ -1300,52 +1344,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2585.660170876755</v>
+        <v>2033.129882347669</v>
       </c>
       <c r="G15" t="n">
-        <v>769.0077020117004</v>
+        <v>207.9557836837388</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.95340061693116</v>
       </c>
       <c r="M15" t="n">
-        <v>94.22029424815778</v>
+        <v>61.56552117887807</v>
       </c>
       <c r="P15" t="n">
-        <v>66.37576657050361</v>
+        <v>37.29551603969661</v>
       </c>
       <c r="S15" t="n">
-        <v>60.32205156166516</v>
+        <v>76.71484499232108</v>
       </c>
       <c r="V15" t="n">
-        <v>48.47098833263519</v>
+        <v>45.55579218457805</v>
       </c>
       <c r="AH15" t="n">
-        <v>450.6822121799099</v>
+        <v>515.8816877153787</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.431143111703292</v>
+        <v>16.48163882056894</v>
       </c>
       <c r="DK15" t="n">
-        <v>9.812116227448763</v>
+        <v>2.085105047848485</v>
       </c>
       <c r="DO15" t="n">
-        <v>87.99621576168805</v>
+        <v>91.22704051647813</v>
       </c>
       <c r="EC15" t="n">
-        <v>815.1638770886668</v>
+        <v>911.7040342448253</v>
       </c>
       <c r="EF15" t="n">
-        <v>285.7440122104679</v>
+        <v>261.4140265947325</v>
       </c>
       <c r="EO15" t="n">
-        <v>19.0204178615859</v>
+        <v>0.7610654058062161</v>
       </c>
       <c r="ER15" t="n">
-        <v>10.91273129686286</v>
+        <v>12.81277237382661</v>
       </c>
       <c r="HL15" t="n">
-        <v>41.02970911872556</v>
+        <v>29.86688102143439</v>
       </c>
       <c r="LA15" t="n">
-        <v>4.714898480864836</v>
+        <v>0.536761424542756</v>
       </c>
     </row>
     <row r="16">
@@ -1360,52 +1407,55 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2843.920665083625</v>
+        <v>1586.899135639093</v>
       </c>
       <c r="G16" t="n">
-        <v>260.9853919341124</v>
+        <v>185.5148588855724</v>
+      </c>
+      <c r="J16" t="n">
+        <v>59.21480419612013</v>
       </c>
       <c r="M16" t="n">
-        <v>22.7752904707209</v>
+        <v>15.77150776347467</v>
       </c>
       <c r="P16" t="n">
-        <v>19.27628953733768</v>
+        <v>29.93912763149383</v>
       </c>
       <c r="S16" t="n">
-        <v>57.81961447194939</v>
+        <v>63.49909547247332</v>
       </c>
       <c r="V16" t="n">
-        <v>35.73140187983635</v>
+        <v>15.15035258354712</v>
       </c>
       <c r="AH16" t="n">
-        <v>670.7750038295401</v>
+        <v>980.799929490098</v>
       </c>
       <c r="AW16" t="n">
-        <v>10.18059942444499</v>
+        <v>9.229879972563905</v>
       </c>
       <c r="DK16" t="n">
-        <v>6.677914091132656</v>
+        <v>7.383376163974785</v>
       </c>
       <c r="DO16" t="n">
-        <v>96.53025760501221</v>
+        <v>27.9905413104678</v>
       </c>
       <c r="EC16" t="n">
-        <v>630.855192041499</v>
+        <v>110.1187847916595</v>
       </c>
       <c r="EF16" t="n">
-        <v>286.964806504013</v>
+        <v>308.2511117603332</v>
       </c>
       <c r="EO16" t="n">
-        <v>18.44532207363297</v>
+        <v>3.001604830156177</v>
       </c>
       <c r="ER16" t="n">
-        <v>7.641180413230286</v>
+        <v>7.750074945157146</v>
       </c>
       <c r="HL16" t="n">
-        <v>77.39342702969766</v>
+        <v>25.37908807369356</v>
       </c>
       <c r="LA16" t="n">
-        <v>2.343196373509872</v>
+        <v>2.588602552918893</v>
       </c>
     </row>
     <row r="17">
@@ -1420,52 +1470,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>697.5799236560691</v>
+        <v>1311.291518709471</v>
       </c>
       <c r="G17" t="n">
-        <v>120.0795405579824</v>
+        <v>581.4659567327172</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.18379262187291</v>
       </c>
       <c r="M17" t="n">
-        <v>67.62296856686413</v>
+        <v>35.24273441003194</v>
       </c>
       <c r="P17" t="n">
-        <v>33.68815813642588</v>
+        <v>67.25685955494775</v>
       </c>
       <c r="S17" t="n">
-        <v>67.52611418230545</v>
+        <v>11.28111011187855</v>
       </c>
       <c r="V17" t="n">
-        <v>13.87923470620655</v>
+        <v>0.4261481141613677</v>
       </c>
       <c r="AH17" t="n">
-        <v>337.3566417928968</v>
+        <v>971.2203597323181</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.919496147574339</v>
+        <v>19.99585315799124</v>
       </c>
       <c r="DK17" t="n">
-        <v>8.925868830632279</v>
+        <v>5.961170481335825</v>
       </c>
       <c r="DO17" t="n">
-        <v>49.03287693403469</v>
+        <v>59.03666259533067</v>
       </c>
       <c r="EC17" t="n">
-        <v>887.3256560000104</v>
+        <v>452.2032300927189</v>
       </c>
       <c r="EF17" t="n">
-        <v>469.7415390477873</v>
+        <v>457.1475444147246</v>
       </c>
       <c r="EO17" t="n">
-        <v>16.73217338811355</v>
+        <v>15.46516222349777</v>
       </c>
       <c r="ER17" t="n">
-        <v>7.784435875424349</v>
+        <v>13.90130040506655</v>
       </c>
       <c r="HL17" t="n">
-        <v>50.37329096164266</v>
+        <v>88.73734185372108</v>
       </c>
       <c r="LA17" t="n">
-        <v>3.561593707273945</v>
+        <v>2.152148031411535</v>
       </c>
     </row>
     <row r="18">
@@ -1480,52 +1533,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2775.423008981461</v>
+        <v>1426.273971590609</v>
       </c>
       <c r="G18" t="n">
-        <v>782.5378422083298</v>
+        <v>395.5757567003266</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42.63771146830101</v>
       </c>
       <c r="M18" t="n">
-        <v>42.45334611948629</v>
+        <v>91.74759424507508</v>
       </c>
       <c r="P18" t="n">
-        <v>99.13311421880049</v>
+        <v>90.60198830246701</v>
       </c>
       <c r="S18" t="n">
-        <v>65.41965541401947</v>
+        <v>47.66693395841779</v>
       </c>
       <c r="V18" t="n">
-        <v>49.06449703258133</v>
+        <v>6.668071736252573</v>
       </c>
       <c r="AH18" t="n">
-        <v>694.3670340580954</v>
+        <v>92.53734428618354</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.095152204259966</v>
+        <v>3.894759413829341</v>
       </c>
       <c r="DK18" t="n">
-        <v>8.956170135972393</v>
+        <v>5.401372007709666</v>
       </c>
       <c r="DO18" t="n">
-        <v>45.69719597555012</v>
+        <v>43.61659596360207</v>
       </c>
       <c r="EC18" t="n">
-        <v>718.0038775982301</v>
+        <v>958.8798292872854</v>
       </c>
       <c r="EF18" t="n">
-        <v>440.3464401948108</v>
+        <v>8.660200856263401</v>
       </c>
       <c r="EO18" t="n">
-        <v>4.825994256880946</v>
+        <v>13.09628371345474</v>
       </c>
       <c r="ER18" t="n">
-        <v>17.30029595692371</v>
+        <v>8.67196006968333</v>
       </c>
       <c r="HL18" t="n">
-        <v>62.77777324073902</v>
+        <v>54.84350997578041</v>
       </c>
       <c r="LA18" t="n">
-        <v>1.520621194262765</v>
+        <v>3.208679947860022</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1596,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1937.296689155379</v>
+        <v>358.8964632755541</v>
       </c>
       <c r="G19" t="n">
-        <v>122.5109007179962</v>
+        <v>372.4518718514851</v>
+      </c>
+      <c r="J19" t="n">
+        <v>63.51899631286892</v>
       </c>
       <c r="M19" t="n">
-        <v>69.09842164928091</v>
+        <v>19.97543402240405</v>
       </c>
       <c r="P19" t="n">
-        <v>13.25156103547785</v>
+        <v>68.96041368717708</v>
       </c>
       <c r="S19" t="n">
-        <v>10.22344889273717</v>
+        <v>52.92636639702043</v>
       </c>
       <c r="V19" t="n">
-        <v>9.869157093822039</v>
+        <v>40.93309410470248</v>
       </c>
       <c r="AH19" t="n">
-        <v>414.6333937612266</v>
+        <v>767.6654019579387</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.83578000166187</v>
+        <v>11.13817812564904</v>
       </c>
       <c r="DK19" t="n">
-        <v>8.483522586814269</v>
+        <v>9.949871120859434</v>
       </c>
       <c r="DO19" t="n">
-        <v>30.42119370085743</v>
+        <v>63.15474648627705</v>
       </c>
       <c r="EC19" t="n">
-        <v>268.9968415627245</v>
+        <v>832.5232112891013</v>
       </c>
       <c r="EF19" t="n">
-        <v>63.60346623461122</v>
+        <v>38.17815017576586</v>
       </c>
       <c r="EO19" t="n">
-        <v>0.6887272577900561</v>
+        <v>4.923258775725126</v>
       </c>
       <c r="ER19" t="n">
-        <v>3.616695380342985</v>
+        <v>17.63554527065445</v>
       </c>
       <c r="HL19" t="n">
-        <v>75.31631919755351</v>
+        <v>44.19692885560706</v>
       </c>
       <c r="LA19" t="n">
-        <v>4.36499379031749</v>
+        <v>1.444658921630274</v>
       </c>
     </row>
     <row r="20">
@@ -1600,52 +1659,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2226.741134925854</v>
+        <v>1022.551886714328</v>
       </c>
       <c r="G20" t="n">
-        <v>593.4970020933957</v>
+        <v>573.9845649706697</v>
+      </c>
+      <c r="J20" t="n">
+        <v>49.45638416194647</v>
       </c>
       <c r="M20" t="n">
-        <v>55.4888432567267</v>
+        <v>99.77929993433753</v>
       </c>
       <c r="P20" t="n">
-        <v>0.07459498604928116</v>
+        <v>58.06698185784072</v>
       </c>
       <c r="S20" t="n">
-        <v>78.57606454796903</v>
+        <v>77.91496406249128</v>
       </c>
       <c r="V20" t="n">
-        <v>17.92810224615852</v>
+        <v>12.12181618607159</v>
       </c>
       <c r="AH20" t="n">
-        <v>534.0415204225953</v>
+        <v>303.704046715319</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.23693491922639</v>
+        <v>17.12747626737926</v>
       </c>
       <c r="DK20" t="n">
-        <v>0.7067769393655376</v>
+        <v>9.768707923384204</v>
       </c>
       <c r="DO20" t="n">
-        <v>74.42721178590661</v>
+        <v>86.67068428525123</v>
       </c>
       <c r="EC20" t="n">
-        <v>746.8812366419762</v>
+        <v>78.29163674772089</v>
       </c>
       <c r="EF20" t="n">
-        <v>11.02022070799446</v>
+        <v>145.5577005548838</v>
       </c>
       <c r="EO20" t="n">
-        <v>2.493870634116775</v>
+        <v>11.19555872404844</v>
       </c>
       <c r="ER20" t="n">
-        <v>6.982395970552946</v>
+        <v>3.246507235754514</v>
       </c>
       <c r="HL20" t="n">
-        <v>41.4732713071417</v>
+        <v>97.17255186993032</v>
       </c>
       <c r="LA20" t="n">
-        <v>0.9950069973705189</v>
+        <v>4.904231047293035</v>
       </c>
     </row>
     <row r="21">
@@ -1660,52 +1722,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1605.179656915333</v>
+        <v>2808.968810199797</v>
       </c>
       <c r="G21" t="n">
-        <v>391.708162733486</v>
+        <v>567.2794733036296</v>
+      </c>
+      <c r="J21" t="n">
+        <v>85.64772068704785</v>
       </c>
       <c r="M21" t="n">
-        <v>65.87987383422001</v>
+        <v>87.21779724240581</v>
       </c>
       <c r="P21" t="n">
-        <v>55.26408382744922</v>
+        <v>64.61282593759806</v>
       </c>
       <c r="S21" t="n">
-        <v>80.94686523429107</v>
+        <v>64.50642710784678</v>
       </c>
       <c r="V21" t="n">
-        <v>16.84685214077597</v>
+        <v>16.35040715084857</v>
       </c>
       <c r="AH21" t="n">
-        <v>682.2021967666865</v>
+        <v>447.226005791818</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.629492826523595</v>
+        <v>2.679410684062706</v>
       </c>
       <c r="DK21" t="n">
-        <v>7.769487361587897</v>
+        <v>1.985132601210804</v>
       </c>
       <c r="DO21" t="n">
-        <v>42.74893790151575</v>
+        <v>14.43016081450014</v>
       </c>
       <c r="EC21" t="n">
-        <v>366.6846371718369</v>
+        <v>601.5908373761633</v>
       </c>
       <c r="EF21" t="n">
-        <v>215.5310026781177</v>
+        <v>85.35382816422089</v>
       </c>
       <c r="EO21" t="n">
-        <v>7.88106405071521</v>
+        <v>8.912027883344207</v>
       </c>
       <c r="ER21" t="n">
-        <v>0.6982974715287771</v>
+        <v>3.882913337152694</v>
       </c>
       <c r="HL21" t="n">
-        <v>91.78018598114204</v>
+        <v>71.70305319997867</v>
       </c>
       <c r="LA21" t="n">
-        <v>3.976692660128598</v>
+        <v>4.30321082149147</v>
       </c>
     </row>
     <row r="22">
@@ -1720,52 +1785,55 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1159.279373390081</v>
+        <v>2661.783238367573</v>
       </c>
       <c r="G22" t="n">
-        <v>374.2024787849066</v>
+        <v>477.0968825131957</v>
+      </c>
+      <c r="J22" t="n">
+        <v>80.35654298267745</v>
       </c>
       <c r="M22" t="n">
-        <v>37.74333782555571</v>
+        <v>97.52118205481884</v>
       </c>
       <c r="P22" t="n">
-        <v>10.87276243519475</v>
+        <v>96.71621614802226</v>
       </c>
       <c r="S22" t="n">
-        <v>9.406747087030876</v>
+        <v>35.93739198575431</v>
       </c>
       <c r="V22" t="n">
-        <v>8.081534376375487</v>
+        <v>0.1455436262120857</v>
       </c>
       <c r="AH22" t="n">
-        <v>680.0733966883313</v>
+        <v>107.724719643447</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.149003296419354</v>
+        <v>13.50371281151836</v>
       </c>
       <c r="DK22" t="n">
-        <v>5.747730440173139</v>
+        <v>6.449888270782659</v>
       </c>
       <c r="DO22" t="n">
-        <v>23.78115428812067</v>
+        <v>7.530224101248439</v>
       </c>
       <c r="EC22" t="n">
-        <v>654.1364607595326</v>
+        <v>754.6713307881199</v>
       </c>
       <c r="EF22" t="n">
-        <v>443.132906503373</v>
+        <v>428.2640071219533</v>
       </c>
       <c r="EO22" t="n">
-        <v>16.82516638418052</v>
+        <v>12.81261687773778</v>
       </c>
       <c r="ER22" t="n">
-        <v>7.726820762015776</v>
+        <v>4.415415378186549</v>
       </c>
       <c r="HL22" t="n">
-        <v>14.31887091233003</v>
+        <v>84.54871037155969</v>
       </c>
       <c r="LA22" t="n">
-        <v>0.9566513512141328</v>
+        <v>3.605336393158687</v>
       </c>
     </row>
     <row r="23">
@@ -1780,52 +1848,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>865.7912032844786</v>
+        <v>2658.960520063588</v>
       </c>
       <c r="G23" t="n">
-        <v>540.291805235507</v>
+        <v>524.6700157323372</v>
+      </c>
+      <c r="J23" t="n">
+        <v>91.66769207798789</v>
       </c>
       <c r="M23" t="n">
-        <v>74.52868516523242</v>
+        <v>8.998131556563315</v>
       </c>
       <c r="P23" t="n">
-        <v>46.13855252066498</v>
+        <v>7.34138144496046</v>
       </c>
       <c r="S23" t="n">
-        <v>36.95123792713759</v>
+        <v>92.82288493255177</v>
       </c>
       <c r="V23" t="n">
-        <v>10.68338715198035</v>
+        <v>25.32981448480378</v>
       </c>
       <c r="AH23" t="n">
-        <v>944.4552527988869</v>
+        <v>781.0295648241461</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.241602021196567</v>
+        <v>14.42799819558425</v>
       </c>
       <c r="DK23" t="n">
-        <v>1.897607380432629</v>
+        <v>9.027775200008545</v>
       </c>
       <c r="DO23" t="n">
-        <v>78.44051115187317</v>
+        <v>56.06173845745954</v>
       </c>
       <c r="EC23" t="n">
-        <v>484.2948133754359</v>
+        <v>992.110461197412</v>
       </c>
       <c r="EF23" t="n">
-        <v>438.6933117466292</v>
+        <v>110.4403322134752</v>
       </c>
       <c r="EO23" t="n">
-        <v>10.21041279420144</v>
+        <v>12.0008093772919</v>
       </c>
       <c r="ER23" t="n">
-        <v>2.825732109332724</v>
+        <v>0.1138771048793719</v>
       </c>
       <c r="HL23" t="n">
-        <v>71.10943542366839</v>
+        <v>32.59774917165485</v>
       </c>
       <c r="LA23" t="n">
-        <v>3.367092121105546</v>
+        <v>0.6926731985692347</v>
       </c>
     </row>
     <row r="24">
@@ -1840,52 +1911,55 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>139.9899348086508</v>
+        <v>2010.436822369763</v>
       </c>
       <c r="G24" t="n">
-        <v>203.7908061528565</v>
+        <v>381.46719071166</v>
+      </c>
+      <c r="J24" t="n">
+        <v>38.68217986524458</v>
       </c>
       <c r="M24" t="n">
-        <v>51.72497751085972</v>
+        <v>0.1302172788317901</v>
       </c>
       <c r="P24" t="n">
-        <v>49.9293011426846</v>
+        <v>40.36263180519115</v>
       </c>
       <c r="S24" t="n">
-        <v>30.59061775620044</v>
+        <v>91.44344002516789</v>
       </c>
       <c r="V24" t="n">
-        <v>49.29919668645041</v>
+        <v>34.05025859273685</v>
       </c>
       <c r="AH24" t="n">
-        <v>111.410647861196</v>
+        <v>634.0411775994021</v>
       </c>
       <c r="AW24" t="n">
-        <v>19.08436975460509</v>
+        <v>19.20480090367142</v>
       </c>
       <c r="DK24" t="n">
-        <v>7.700594915832743</v>
+        <v>1.887006568484295</v>
       </c>
       <c r="DO24" t="n">
-        <v>70.58814683623744</v>
+        <v>10.61002357440606</v>
       </c>
       <c r="EC24" t="n">
-        <v>46.29831874689438</v>
+        <v>898.6066927258788</v>
       </c>
       <c r="EF24" t="n">
-        <v>67.99273447900056</v>
+        <v>226.0745009506724</v>
       </c>
       <c r="EO24" t="n">
-        <v>13.07785229747113</v>
+        <v>1.773428576852423</v>
       </c>
       <c r="ER24" t="n">
-        <v>8.660453962939469</v>
+        <v>8.711586925778702</v>
       </c>
       <c r="HL24" t="n">
-        <v>36.55241039414783</v>
+        <v>86.48034512210153</v>
       </c>
       <c r="LA24" t="n">
-        <v>1.07057101549378</v>
+        <v>3.767601659256182</v>
       </c>
     </row>
     <row r="25">
@@ -1900,52 +1974,55 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1463.756222380202</v>
+        <v>1926.695630447313</v>
       </c>
       <c r="G25" t="n">
-        <v>32.18150720532256</v>
+        <v>585.2217890334399</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8.57154877635552</v>
       </c>
       <c r="M25" t="n">
-        <v>74.56089735847094</v>
+        <v>5.757790231501103</v>
       </c>
       <c r="P25" t="n">
-        <v>10.02724482952949</v>
+        <v>45.83813908492963</v>
       </c>
       <c r="S25" t="n">
-        <v>22.11534631811768</v>
+        <v>57.19443070968426</v>
       </c>
       <c r="V25" t="n">
-        <v>6.781129966698829</v>
+        <v>26.64524233295997</v>
       </c>
       <c r="AH25" t="n">
-        <v>44.85047304243228</v>
+        <v>542.8237092288647</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.728310794472935</v>
+        <v>9.423191080060803</v>
       </c>
       <c r="DK25" t="n">
-        <v>6.176916961573998</v>
+        <v>9.218171015674137</v>
       </c>
       <c r="DO25" t="n">
-        <v>73.56320152705777</v>
+        <v>35.94363031848828</v>
       </c>
       <c r="EC25" t="n">
-        <v>804.1730858258632</v>
+        <v>678.893470307617</v>
       </c>
       <c r="EF25" t="n">
-        <v>113.876801007072</v>
+        <v>219.9174768993831</v>
       </c>
       <c r="EO25" t="n">
-        <v>12.15389030199425</v>
+        <v>18.66295377199039</v>
       </c>
       <c r="ER25" t="n">
-        <v>19.72718535476899</v>
+        <v>3.784154935157242</v>
       </c>
       <c r="HL25" t="n">
-        <v>9.908464412912465</v>
+        <v>59.71288665908308</v>
       </c>
       <c r="LA25" t="n">
-        <v>0.9774087650645458</v>
+        <v>0.5053804320032901</v>
       </c>
     </row>
     <row r="26">
@@ -1960,52 +2037,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71.97662264907068</v>
+        <v>964.6841174730977</v>
       </c>
       <c r="G26" t="n">
-        <v>370.3284665165077</v>
+        <v>399.6449229581409</v>
+      </c>
+      <c r="J26" t="n">
+        <v>96.30901828334994</v>
       </c>
       <c r="M26" t="n">
-        <v>95.52712103444296</v>
+        <v>90.39362117047115</v>
       </c>
       <c r="P26" t="n">
-        <v>31.55354727941831</v>
+        <v>50.28824493572367</v>
       </c>
       <c r="S26" t="n">
-        <v>95.14678345415562</v>
+        <v>66.35932044045828</v>
       </c>
       <c r="V26" t="n">
-        <v>25.52113015984754</v>
+        <v>35.24031352698265</v>
       </c>
       <c r="AH26" t="n">
-        <v>206.5541402026861</v>
+        <v>778.6934755962371</v>
       </c>
       <c r="AW26" t="n">
-        <v>16.41858590691338</v>
+        <v>5.690747502186923</v>
       </c>
       <c r="DK26" t="n">
-        <v>6.580910152455309</v>
+        <v>8.870909117457135</v>
       </c>
       <c r="DO26" t="n">
-        <v>84.97842952511363</v>
+        <v>45.28892928747942</v>
       </c>
       <c r="EC26" t="n">
-        <v>713.9695971015848</v>
+        <v>457.8664595801042</v>
       </c>
       <c r="EF26" t="n">
-        <v>431.6707630478141</v>
+        <v>394.5945904712563</v>
       </c>
       <c r="EO26" t="n">
-        <v>12.76833437062753</v>
+        <v>1.038547739908287</v>
       </c>
       <c r="ER26" t="n">
-        <v>12.06186224237481</v>
+        <v>6.77543213395788</v>
       </c>
       <c r="HL26" t="n">
-        <v>32.83894651971527</v>
+        <v>37.58901567895671</v>
       </c>
       <c r="LA26" t="n">
-        <v>0.1225384297192234</v>
+        <v>2.228648065446275</v>
       </c>
     </row>
     <row r="27">
@@ -2020,52 +2100,55 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>585.1169897494528</v>
+        <v>848.6195021893293</v>
       </c>
       <c r="G27" t="n">
-        <v>737.5664312389167</v>
+        <v>580.1045204065742</v>
+      </c>
+      <c r="J27" t="n">
+        <v>51.22370309574059</v>
       </c>
       <c r="M27" t="n">
-        <v>81.95384413678973</v>
+        <v>88.43313536009255</v>
       </c>
       <c r="P27" t="n">
-        <v>86.64058667153188</v>
+        <v>79.24235123548392</v>
       </c>
       <c r="S27" t="n">
-        <v>7.13484756413576</v>
+        <v>31.8319004017992</v>
       </c>
       <c r="V27" t="n">
-        <v>30.79526650193215</v>
+        <v>14.57534301291777</v>
       </c>
       <c r="AH27" t="n">
-        <v>422.2081442653012</v>
+        <v>463.6812388422149</v>
       </c>
       <c r="AW27" t="n">
-        <v>11.08608099082089</v>
+        <v>1.9230128725421</v>
       </c>
       <c r="DK27" t="n">
-        <v>6.902514587156732</v>
+        <v>7.546848799282521</v>
       </c>
       <c r="DO27" t="n">
-        <v>53.94750991572087</v>
+        <v>35.16933514683078</v>
       </c>
       <c r="EC27" t="n">
-        <v>968.7776103413839</v>
+        <v>60.9248976736273</v>
       </c>
       <c r="EF27" t="n">
-        <v>214.2659809744636</v>
+        <v>15.81114760846614</v>
       </c>
       <c r="EO27" t="n">
-        <v>11.03919760938195</v>
+        <v>3.039280534690916</v>
       </c>
       <c r="ER27" t="n">
-        <v>16.25717288086149</v>
+        <v>18.82161506048469</v>
       </c>
       <c r="HL27" t="n">
-        <v>32.7759231485996</v>
+        <v>13.78850489665613</v>
       </c>
       <c r="LA27" t="n">
-        <v>2.198343110032484</v>
+        <v>0.9713898847172897</v>
       </c>
     </row>
     <row r="28">
@@ -2080,52 +2163,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2231.685989634252</v>
+        <v>2743.305949989509</v>
       </c>
       <c r="G28" t="n">
-        <v>781.5161647795666</v>
+        <v>775.1142430963145</v>
+      </c>
+      <c r="J28" t="n">
+        <v>51.26912379104252</v>
       </c>
       <c r="M28" t="n">
-        <v>50.73285922157999</v>
+        <v>69.06638336573107</v>
       </c>
       <c r="P28" t="n">
-        <v>38.67771561042754</v>
+        <v>47.26481568405515</v>
       </c>
       <c r="S28" t="n">
-        <v>10.40076601901645</v>
+        <v>84.15208170148503</v>
       </c>
       <c r="V28" t="n">
-        <v>34.8148506154775</v>
+        <v>24.62117663687409</v>
       </c>
       <c r="AH28" t="n">
-        <v>543.5296663826543</v>
+        <v>851.003349796352</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.64464516354654</v>
+        <v>15.8602953740878</v>
       </c>
       <c r="DK28" t="n">
-        <v>8.291022570334009</v>
+        <v>4.806301989994635</v>
       </c>
       <c r="DO28" t="n">
-        <v>92.25057275122109</v>
+        <v>7.292475155653033</v>
       </c>
       <c r="EC28" t="n">
-        <v>540.3461850450863</v>
+        <v>416.0690204989773</v>
       </c>
       <c r="EF28" t="n">
-        <v>380.9159998216786</v>
+        <v>130.8487222021302</v>
       </c>
       <c r="EO28" t="n">
-        <v>0.7737228792673467</v>
+        <v>18.2326754635293</v>
       </c>
       <c r="ER28" t="n">
-        <v>15.65341002963838</v>
+        <v>19.01103847804401</v>
       </c>
       <c r="HL28" t="n">
-        <v>80.33000561987519</v>
+        <v>1.019309543220737</v>
       </c>
       <c r="LA28" t="n">
-        <v>0.1326507051206705</v>
+        <v>1.490660170616784</v>
       </c>
     </row>
     <row r="29">
@@ -2140,52 +2226,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>562.5536054808116</v>
+        <v>1909.132566743738</v>
       </c>
       <c r="G29" t="n">
-        <v>695.4468404213939</v>
+        <v>355.7846120514619</v>
+      </c>
+      <c r="J29" t="n">
+        <v>83.10908997093516</v>
       </c>
       <c r="M29" t="n">
-        <v>50.19382486042338</v>
+        <v>5.08609698342215</v>
       </c>
       <c r="P29" t="n">
-        <v>37.9148741897136</v>
+        <v>69.81694457829784</v>
       </c>
       <c r="S29" t="n">
-        <v>41.95156083648494</v>
+        <v>81.8825366831917</v>
       </c>
       <c r="V29" t="n">
-        <v>15.03572297822056</v>
+        <v>13.71495478576594</v>
       </c>
       <c r="AH29" t="n">
-        <v>628.2376449222093</v>
+        <v>882.9646109046145</v>
       </c>
       <c r="AW29" t="n">
-        <v>10.52010201314448</v>
+        <v>5.289417266088212</v>
       </c>
       <c r="DK29" t="n">
-        <v>3.141693434005539</v>
+        <v>9.071483385007298</v>
       </c>
       <c r="DO29" t="n">
-        <v>77.0470573425311</v>
+        <v>19.64233726915832</v>
       </c>
       <c r="EC29" t="n">
-        <v>979.0057894003171</v>
+        <v>543.2866749810514</v>
       </c>
       <c r="EF29" t="n">
-        <v>143.8841409622633</v>
+        <v>47.53355220521493</v>
       </c>
       <c r="EO29" t="n">
-        <v>0.7021126199564787</v>
+        <v>11.16090427434651</v>
       </c>
       <c r="ER29" t="n">
-        <v>16.52267797317694</v>
+        <v>5.740498458952192</v>
       </c>
       <c r="HL29" t="n">
-        <v>42.62050323587437</v>
+        <v>68.50215609678337</v>
       </c>
       <c r="LA29" t="n">
-        <v>1.820555582988784</v>
+        <v>0.3742987735528641</v>
       </c>
     </row>
     <row r="30">
@@ -2200,52 +2289,55 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1155.436629346815</v>
+        <v>1587.368093124346</v>
       </c>
       <c r="G30" t="n">
-        <v>125.415014586524</v>
+        <v>231.6304860768819</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4956651114102484</v>
       </c>
       <c r="M30" t="n">
-        <v>81.75127222868048</v>
+        <v>53.82149162887595</v>
       </c>
       <c r="P30" t="n">
-        <v>84.49681619997881</v>
+        <v>3.20878891541011</v>
       </c>
       <c r="S30" t="n">
-        <v>87.87992388695935</v>
+        <v>63.96062747751178</v>
       </c>
       <c r="V30" t="n">
-        <v>3.679987697483389</v>
+        <v>24.79140496289605</v>
       </c>
       <c r="AH30" t="n">
-        <v>182.2593063378363</v>
+        <v>606.0106709791461</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.156384891379776</v>
+        <v>6.890570920287848</v>
       </c>
       <c r="DK30" t="n">
-        <v>6.153622380404792</v>
+        <v>2.7818643063444</v>
       </c>
       <c r="DO30" t="n">
-        <v>66.8622502352915</v>
+        <v>55.36142956364966</v>
       </c>
       <c r="EC30" t="n">
-        <v>448.0871275084989</v>
+        <v>350.466289993866</v>
       </c>
       <c r="EF30" t="n">
-        <v>269.8872817924722</v>
+        <v>295.0846600519105</v>
       </c>
       <c r="EO30" t="n">
-        <v>17.92074565245995</v>
+        <v>5.201085106114569</v>
       </c>
       <c r="ER30" t="n">
-        <v>15.10147397288566</v>
+        <v>7.589667018446475</v>
       </c>
       <c r="HL30" t="n">
-        <v>87.32649577431384</v>
+        <v>14.27980425558596</v>
       </c>
       <c r="LA30" t="n">
-        <v>2.673773861394686</v>
+        <v>4.809760001747897</v>
       </c>
     </row>
     <row r="31">
@@ -2260,52 +2352,55 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2467.757144289608</v>
+        <v>1082.024466378306</v>
       </c>
       <c r="G31" t="n">
-        <v>468.8151680742632</v>
+        <v>496.3407444214588</v>
+      </c>
+      <c r="J31" t="n">
+        <v>39.11315085696607</v>
       </c>
       <c r="M31" t="n">
-        <v>38.8535480263731</v>
+        <v>23.82370118464377</v>
       </c>
       <c r="P31" t="n">
-        <v>26.16798025428434</v>
+        <v>55.31075775664186</v>
       </c>
       <c r="S31" t="n">
-        <v>75.37755080386381</v>
+        <v>18.94426589139409</v>
       </c>
       <c r="V31" t="n">
-        <v>14.05043243202932</v>
+        <v>5.066558822447203</v>
       </c>
       <c r="AH31" t="n">
-        <v>597.2511427823717</v>
+        <v>927.2642900324979</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.776952757024045</v>
+        <v>10.49487047866364</v>
       </c>
       <c r="DK31" t="n">
-        <v>6.504335009961849</v>
+        <v>6.581503626572252</v>
       </c>
       <c r="DO31" t="n">
-        <v>28.25510946039702</v>
+        <v>79.87503436789176</v>
       </c>
       <c r="EC31" t="n">
-        <v>714.3072168417011</v>
+        <v>537.5097023111216</v>
       </c>
       <c r="EF31" t="n">
-        <v>281.4114150203179</v>
+        <v>57.59601813663645</v>
       </c>
       <c r="EO31" t="n">
-        <v>1.679431196043837</v>
+        <v>8.790733617976214</v>
       </c>
       <c r="ER31" t="n">
-        <v>1.395974411637404</v>
+        <v>3.102854301386955</v>
       </c>
       <c r="HL31" t="n">
-        <v>97.52369673051454</v>
+        <v>7.960235448508457</v>
       </c>
       <c r="LA31" t="n">
-        <v>3.02448520143058</v>
+        <v>1.190934960783252</v>
       </c>
     </row>
     <row r="32">
@@ -2320,52 +2415,55 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2141.700714283498</v>
+        <v>107.9665736748007</v>
       </c>
       <c r="G32" t="n">
-        <v>364.0339728919888</v>
+        <v>550.130680242581</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.462663940793098</v>
       </c>
       <c r="M32" t="n">
-        <v>2.977621303858036</v>
+        <v>90.4460622364634</v>
       </c>
       <c r="P32" t="n">
-        <v>46.10161258329121</v>
+        <v>42.03479073170116</v>
       </c>
       <c r="S32" t="n">
-        <v>91.67953388756084</v>
+        <v>68.60288247374667</v>
       </c>
       <c r="V32" t="n">
-        <v>39.10486515403881</v>
+        <v>17.5903489943038</v>
       </c>
       <c r="AH32" t="n">
-        <v>164.4262029543235</v>
+        <v>998.6452641992173</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.255076420168704</v>
+        <v>8.021867554647656</v>
       </c>
       <c r="DK32" t="n">
-        <v>2.096565215906558</v>
+        <v>9.652022384688298</v>
       </c>
       <c r="DO32" t="n">
-        <v>64.14458049895904</v>
+        <v>41.52903543472573</v>
       </c>
       <c r="EC32" t="n">
-        <v>582.5811257945071</v>
+        <v>143.4294268298768</v>
       </c>
       <c r="EF32" t="n">
-        <v>78.55608057069435</v>
+        <v>446.1905312087447</v>
       </c>
       <c r="EO32" t="n">
-        <v>18.94237320908534</v>
+        <v>4.195692455843087</v>
       </c>
       <c r="ER32" t="n">
-        <v>3.203077715609719</v>
+        <v>19.27914306916967</v>
       </c>
       <c r="HL32" t="n">
-        <v>47.84283341004981</v>
+        <v>53.45419832982038</v>
       </c>
       <c r="LA32" t="n">
-        <v>0.3608206230664879</v>
+        <v>1.768888398007683</v>
       </c>
     </row>
     <row r="33">
@@ -2380,52 +2478,55 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2894.991083504532</v>
+        <v>697.0448447361997</v>
       </c>
       <c r="G33" t="n">
-        <v>589.6460904784814</v>
+        <v>100.0520032714622</v>
+      </c>
+      <c r="J33" t="n">
+        <v>26.92474091582755</v>
       </c>
       <c r="M33" t="n">
-        <v>11.22269145554848</v>
+        <v>46.14315601573975</v>
       </c>
       <c r="P33" t="n">
-        <v>15.9968561870706</v>
+        <v>7.700978149343529</v>
       </c>
       <c r="S33" t="n">
-        <v>5.306240412293539</v>
+        <v>11.3693427102141</v>
       </c>
       <c r="V33" t="n">
-        <v>6.30233743361413</v>
+        <v>11.80475389561745</v>
       </c>
       <c r="AH33" t="n">
-        <v>402.5649412142026</v>
+        <v>70.95068352577549</v>
       </c>
       <c r="AW33" t="n">
-        <v>11.97167502594872</v>
+        <v>1.629172567969137</v>
       </c>
       <c r="DK33" t="n">
-        <v>8.414305568377992</v>
+        <v>9.22283829757032</v>
       </c>
       <c r="DO33" t="n">
-        <v>82.4142838646321</v>
+        <v>95.62202177999444</v>
       </c>
       <c r="EC33" t="n">
-        <v>333.3259890758008</v>
+        <v>174.5265363813949</v>
       </c>
       <c r="EF33" t="n">
-        <v>106.4995536186061</v>
+        <v>286.0368218217473</v>
       </c>
       <c r="EO33" t="n">
-        <v>0.1701455307080035</v>
+        <v>10.70285372759215</v>
       </c>
       <c r="ER33" t="n">
-        <v>19.20625440348254</v>
+        <v>2.917502126928433</v>
       </c>
       <c r="HL33" t="n">
-        <v>43.81368390341839</v>
+        <v>9.231140753328759</v>
       </c>
       <c r="LA33" t="n">
-        <v>3.797461912039253</v>
+        <v>1.073783215885294</v>
       </c>
     </row>
     <row r="34">
@@ -2440,52 +2541,55 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1409.025822596568</v>
+        <v>2948.579691780374</v>
       </c>
       <c r="G34" t="n">
-        <v>522.3045689971872</v>
+        <v>120.7575431278801</v>
+      </c>
+      <c r="J34" t="n">
+        <v>95.04285357715517</v>
       </c>
       <c r="M34" t="n">
-        <v>7.047517860500829</v>
+        <v>25.64072029826907</v>
       </c>
       <c r="P34" t="n">
-        <v>11.01943935492062</v>
+        <v>80.14914704249438</v>
       </c>
       <c r="S34" t="n">
-        <v>23.47097210303172</v>
+        <v>75.78261598103542</v>
       </c>
       <c r="V34" t="n">
-        <v>12.6867763230647</v>
+        <v>23.12256249366417</v>
       </c>
       <c r="AH34" t="n">
-        <v>192.1617793006661</v>
+        <v>927.2254114325245</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.055041050494642</v>
+        <v>5.802774360026763</v>
       </c>
       <c r="DK34" t="n">
-        <v>1.052108752425364</v>
+        <v>7.919529182414036</v>
       </c>
       <c r="DO34" t="n">
-        <v>12.22997975566991</v>
+        <v>85.44708375584362</v>
       </c>
       <c r="EC34" t="n">
-        <v>869.6983756300757</v>
+        <v>815.8192022776454</v>
       </c>
       <c r="EF34" t="n">
-        <v>72.56699077342694</v>
+        <v>219.9947867861678</v>
       </c>
       <c r="EO34" t="n">
-        <v>7.964053151657309</v>
+        <v>9.479976193662583</v>
       </c>
       <c r="ER34" t="n">
-        <v>9.599021561523111</v>
+        <v>5.885968665556584</v>
       </c>
       <c r="HL34" t="n">
-        <v>33.66018756433186</v>
+        <v>67.1977549512843</v>
       </c>
       <c r="LA34" t="n">
-        <v>1.856116693636444</v>
+        <v>2.263932048396197</v>
       </c>
     </row>
     <row r="35">
@@ -2500,52 +2604,55 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>168.4839489514122</v>
+        <v>2071.749697470983</v>
       </c>
       <c r="G35" t="n">
-        <v>200.3362419007886</v>
+        <v>596.329411473745</v>
+      </c>
+      <c r="J35" t="n">
+        <v>12.11568905794386</v>
       </c>
       <c r="M35" t="n">
-        <v>24.04844439142549</v>
+        <v>70.02302744608177</v>
       </c>
       <c r="P35" t="n">
-        <v>52.57616828081694</v>
+        <v>53.15377584426292</v>
       </c>
       <c r="S35" t="n">
-        <v>95.87977831253129</v>
+        <v>63.71210148785779</v>
       </c>
       <c r="V35" t="n">
-        <v>32.02684849357947</v>
+        <v>20.29885636458016</v>
       </c>
       <c r="AH35" t="n">
-        <v>753.9624258020126</v>
+        <v>249.4605086619414</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.67322272084018</v>
+        <v>19.25491590984126</v>
       </c>
       <c r="DK35" t="n">
-        <v>1.788993499798455</v>
+        <v>3.055338051485175</v>
       </c>
       <c r="DO35" t="n">
-        <v>31.52924527280216</v>
+        <v>12.18321696193496</v>
       </c>
       <c r="EC35" t="n">
-        <v>323.0224836269078</v>
+        <v>312.0576801546085</v>
       </c>
       <c r="EF35" t="n">
-        <v>464.900057348592</v>
+        <v>33.96206620547365</v>
       </c>
       <c r="EO35" t="n">
-        <v>19.94636725659247</v>
+        <v>19.11071050944077</v>
       </c>
       <c r="ER35" t="n">
-        <v>13.06021457485977</v>
+        <v>12.31582815140792</v>
       </c>
       <c r="HL35" t="n">
-        <v>71.98536557140103</v>
+        <v>66.03735507797501</v>
       </c>
       <c r="LA35" t="n">
-        <v>0.2502586382138239</v>
+        <v>0.5768057929137349</v>
       </c>
     </row>
     <row r="36">
@@ -2560,52 +2667,55 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>708.1094794355807</v>
+        <v>1700.76646015768</v>
       </c>
       <c r="G36" t="n">
-        <v>402.9664327417602</v>
+        <v>290.9720200838518</v>
+      </c>
+      <c r="J36" t="n">
+        <v>67.64743142277861</v>
       </c>
       <c r="M36" t="n">
-        <v>39.89191196069982</v>
+        <v>45.26449053156192</v>
       </c>
       <c r="P36" t="n">
-        <v>11.06060004120791</v>
+        <v>64.03424206980584</v>
       </c>
       <c r="S36" t="n">
-        <v>77.02710863244067</v>
+        <v>44.9686570504041</v>
       </c>
       <c r="V36" t="n">
-        <v>38.53741293351663</v>
+        <v>32.07985158335943</v>
       </c>
       <c r="AH36" t="n">
-        <v>24.96440202173133</v>
+        <v>814.7418322928173</v>
       </c>
       <c r="AW36" t="n">
-        <v>11.63705391388628</v>
+        <v>14.24612029386045</v>
       </c>
       <c r="DK36" t="n">
-        <v>4.005586313355498</v>
+        <v>0.7656904352090677</v>
       </c>
       <c r="DO36" t="n">
-        <v>22.39388768169808</v>
+        <v>33.73427941779602</v>
       </c>
       <c r="EC36" t="n">
-        <v>314.9652075292231</v>
+        <v>513.335325400683</v>
       </c>
       <c r="EF36" t="n">
-        <v>21.65786576594797</v>
+        <v>281.2094151606667</v>
       </c>
       <c r="EO36" t="n">
-        <v>0.3328082199235483</v>
+        <v>7.897581000727572</v>
       </c>
       <c r="ER36" t="n">
-        <v>4.469481183136135</v>
+        <v>1.671462332917195</v>
       </c>
       <c r="HL36" t="n">
-        <v>35.35302182584395</v>
+        <v>21.98092521042476</v>
       </c>
       <c r="LA36" t="n">
-        <v>4.741417549363508</v>
+        <v>3.648196489834531</v>
       </c>
     </row>
     <row r="37">
@@ -2620,52 +2730,55 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>745.1024780123329</v>
+        <v>2138.362995543261</v>
       </c>
       <c r="G37" t="n">
-        <v>97.3698726585111</v>
+        <v>394.1601178618678</v>
+      </c>
+      <c r="J37" t="n">
+        <v>6.831854352163679</v>
       </c>
       <c r="M37" t="n">
-        <v>9.356132902381431</v>
+        <v>80.57636416123727</v>
       </c>
       <c r="P37" t="n">
-        <v>68.32364214812313</v>
+        <v>68.20693722533414</v>
       </c>
       <c r="S37" t="n">
-        <v>5.384010302380371</v>
+        <v>86.18911323686591</v>
       </c>
       <c r="V37" t="n">
-        <v>13.98460579642387</v>
+        <v>34.20547435410579</v>
       </c>
       <c r="AH37" t="n">
-        <v>398.1347531108285</v>
+        <v>241.7791801411028</v>
       </c>
       <c r="AW37" t="n">
-        <v>11.17547756572132</v>
+        <v>19.30401591254742</v>
       </c>
       <c r="DK37" t="n">
-        <v>8.322132949864432</v>
+        <v>3.451110511986807</v>
       </c>
       <c r="DO37" t="n">
-        <v>87.95632895726642</v>
+        <v>24.24404562894465</v>
       </c>
       <c r="EC37" t="n">
-        <v>559.5140392063698</v>
+        <v>896.4146309094606</v>
       </c>
       <c r="EF37" t="n">
-        <v>228.0126701310076</v>
+        <v>378.0132625891912</v>
       </c>
       <c r="EO37" t="n">
-        <v>17.37411652706367</v>
+        <v>3.211044444404985</v>
       </c>
       <c r="ER37" t="n">
-        <v>19.50272709442674</v>
+        <v>8.584079422136819</v>
       </c>
       <c r="HL37" t="n">
-        <v>21.69319324051549</v>
+        <v>46.7437534977681</v>
       </c>
       <c r="LA37" t="n">
-        <v>2.88501076108366</v>
+        <v>1.963612440811326</v>
       </c>
     </row>
     <row r="38">
@@ -2680,52 +2793,55 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2155.027639400467</v>
+        <v>2938.196504655235</v>
       </c>
       <c r="G38" t="n">
-        <v>449.2806397271701</v>
+        <v>534.4713455771631</v>
+      </c>
+      <c r="J38" t="n">
+        <v>38.79745948820174</v>
       </c>
       <c r="M38" t="n">
-        <v>5.624414645351772</v>
+        <v>74.71300777200172</v>
       </c>
       <c r="P38" t="n">
-        <v>77.72542728855848</v>
+        <v>72.69520306718734</v>
       </c>
       <c r="S38" t="n">
-        <v>37.20680941308832</v>
+        <v>60.43332510491075</v>
       </c>
       <c r="V38" t="n">
-        <v>15.43140103409316</v>
+        <v>16.68668472926559</v>
       </c>
       <c r="AH38" t="n">
-        <v>250.7222953136592</v>
+        <v>283.2300910207315</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.286086481321014</v>
+        <v>18.59635366441291</v>
       </c>
       <c r="DK38" t="n">
-        <v>2.943683814341967</v>
+        <v>6.405831013201881</v>
       </c>
       <c r="DO38" t="n">
-        <v>35.65646849450535</v>
+        <v>90.32331301712408</v>
       </c>
       <c r="EC38" t="n">
-        <v>320.3370666371596</v>
+        <v>539.0649796482737</v>
       </c>
       <c r="EF38" t="n">
-        <v>79.24225875607705</v>
+        <v>200.363658839933</v>
       </c>
       <c r="EO38" t="n">
-        <v>15.39778342776162</v>
+        <v>12.05910293542983</v>
       </c>
       <c r="ER38" t="n">
-        <v>12.6063920114847</v>
+        <v>0.1916844049461153</v>
       </c>
       <c r="HL38" t="n">
-        <v>51.97886999634315</v>
+        <v>20.73138855438326</v>
       </c>
       <c r="LA38" t="n">
-        <v>2.427809577006174</v>
+        <v>4.811946000570522</v>
       </c>
     </row>
     <row r="39">
@@ -2740,52 +2856,55 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>61.10373280799364</v>
+        <v>966.765118250407</v>
       </c>
       <c r="G39" t="n">
-        <v>686.6780300915319</v>
+        <v>453.8154323477414</v>
+      </c>
+      <c r="J39" t="n">
+        <v>11.47457470490138</v>
       </c>
       <c r="M39" t="n">
-        <v>15.68113022008467</v>
+        <v>13.56894306762102</v>
       </c>
       <c r="P39" t="n">
-        <v>14.60359937691301</v>
+        <v>71.49766370191503</v>
       </c>
       <c r="S39" t="n">
-        <v>92.49234736394662</v>
+        <v>17.26752596947532</v>
       </c>
       <c r="V39" t="n">
-        <v>29.98206295252434</v>
+        <v>21.89436961198537</v>
       </c>
       <c r="AH39" t="n">
-        <v>427.8433826634184</v>
+        <v>969.9132047540087</v>
       </c>
       <c r="AW39" t="n">
-        <v>6.680250623324864</v>
+        <v>2.6221095898569</v>
       </c>
       <c r="DK39" t="n">
-        <v>8.457907094925089</v>
+        <v>1.575649922896604</v>
       </c>
       <c r="DO39" t="n">
-        <v>49.33093227811997</v>
+        <v>31.53455622415218</v>
       </c>
       <c r="EC39" t="n">
-        <v>276.1867858663425</v>
+        <v>890.0808819002216</v>
       </c>
       <c r="EF39" t="n">
-        <v>329.9822421866814</v>
+        <v>232.2915200847144</v>
       </c>
       <c r="EO39" t="n">
-        <v>13.8330500914112</v>
+        <v>0.1252056636487775</v>
       </c>
       <c r="ER39" t="n">
-        <v>5.891682735010113</v>
+        <v>12.45755377470199</v>
       </c>
       <c r="HL39" t="n">
-        <v>5.671776776070992</v>
+        <v>91.09412452795806</v>
       </c>
       <c r="LA39" t="n">
-        <v>4.765364368297131</v>
+        <v>4.023410793555126</v>
       </c>
     </row>
     <row r="40">
@@ -2800,52 +2919,55 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2115.400281553227</v>
+        <v>524.3161933866414</v>
       </c>
       <c r="G40" t="n">
-        <v>388.8607838311329</v>
+        <v>358.3141712916223</v>
+      </c>
+      <c r="J40" t="n">
+        <v>57.66413629073038</v>
       </c>
       <c r="M40" t="n">
-        <v>24.3642267559406</v>
+        <v>54.18458070342054</v>
       </c>
       <c r="P40" t="n">
-        <v>98.44686797534634</v>
+        <v>45.31333122895649</v>
       </c>
       <c r="S40" t="n">
-        <v>83.61850661527465</v>
+        <v>66.40619481412</v>
       </c>
       <c r="V40" t="n">
-        <v>28.50845487974185</v>
+        <v>44.81775078430621</v>
       </c>
       <c r="AH40" t="n">
-        <v>518.5076140700799</v>
+        <v>230.4425549552112</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.371579911354701</v>
+        <v>7.297591196102213</v>
       </c>
       <c r="DK40" t="n">
-        <v>0.7261956267859826</v>
+        <v>6.66043017546274</v>
       </c>
       <c r="DO40" t="n">
-        <v>15.44589583167378</v>
+        <v>30.19299147146338</v>
       </c>
       <c r="EC40" t="n">
-        <v>777.22067083492</v>
+        <v>8.840776639819525</v>
       </c>
       <c r="EF40" t="n">
-        <v>38.76626806699862</v>
+        <v>478.7460848884365</v>
       </c>
       <c r="EO40" t="n">
-        <v>9.104719497831661</v>
+        <v>11.40616877556028</v>
       </c>
       <c r="ER40" t="n">
-        <v>0.09328540641077021</v>
+        <v>6.485887245469475</v>
       </c>
       <c r="HL40" t="n">
-        <v>52.2099463224916</v>
+        <v>59.02252152128352</v>
       </c>
       <c r="LA40" t="n">
-        <v>2.961877657411982</v>
+        <v>3.559575603633077</v>
       </c>
     </row>
     <row r="41">
@@ -2860,52 +2982,55 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2214.965348919025</v>
+        <v>596.0072370971009</v>
       </c>
       <c r="G41" t="n">
-        <v>607.1261993013809</v>
+        <v>370.0357284402916</v>
+      </c>
+      <c r="J41" t="n">
+        <v>44.24917646665277</v>
       </c>
       <c r="M41" t="n">
-        <v>49.63874037456186</v>
+        <v>98.41149382145183</v>
       </c>
       <c r="P41" t="n">
-        <v>98.74657336104194</v>
+        <v>87.70398253162752</v>
       </c>
       <c r="S41" t="n">
-        <v>23.06052756859109</v>
+        <v>60.91001764484623</v>
       </c>
       <c r="V41" t="n">
-        <v>47.32126490122594</v>
+        <v>46.48808331020086</v>
       </c>
       <c r="AH41" t="n">
-        <v>364.4613255228454</v>
+        <v>589.7302190624368</v>
       </c>
       <c r="AW41" t="n">
-        <v>10.3021179173756</v>
+        <v>17.96195225572426</v>
       </c>
       <c r="DK41" t="n">
-        <v>1.023647533772273</v>
+        <v>3.532806965873416</v>
       </c>
       <c r="DO41" t="n">
-        <v>87.22017157153189</v>
+        <v>25.86212325465549</v>
       </c>
       <c r="EC41" t="n">
-        <v>23.3994034234114</v>
+        <v>603.3210560249098</v>
       </c>
       <c r="EF41" t="n">
-        <v>492.2678871460486</v>
+        <v>16.13908276143733</v>
       </c>
       <c r="EO41" t="n">
-        <v>3.217731644445474</v>
+        <v>16.00803820236493</v>
       </c>
       <c r="ER41" t="n">
-        <v>1.69877707030281</v>
+        <v>14.24765937591159</v>
       </c>
       <c r="HL41" t="n">
-        <v>14.80470262989568</v>
+        <v>42.44005631287521</v>
       </c>
       <c r="LA41" t="n">
-        <v>2.554439362482228</v>
+        <v>0.6331740225291071</v>
       </c>
     </row>
     <row r="42">
@@ -2920,52 +3045,55 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1491.129584106166</v>
+        <v>1890.837464296201</v>
       </c>
       <c r="G42" t="n">
-        <v>723.2985138786318</v>
+        <v>332.5273261267123</v>
+      </c>
+      <c r="J42" t="n">
+        <v>27.99100513315286</v>
       </c>
       <c r="M42" t="n">
-        <v>4.417830805546153</v>
+        <v>49.31402655326769</v>
       </c>
       <c r="P42" t="n">
-        <v>99.44282173985114</v>
+        <v>47.18069227457499</v>
       </c>
       <c r="S42" t="n">
-        <v>91.02909839905037</v>
+        <v>22.34070909112725</v>
       </c>
       <c r="V42" t="n">
-        <v>36.20367098740323</v>
+        <v>5.431679736805789</v>
       </c>
       <c r="AH42" t="n">
-        <v>430.824987189268</v>
+        <v>923.5264831405964</v>
       </c>
       <c r="AW42" t="n">
-        <v>10.32894391146403</v>
+        <v>6.963554073009266</v>
       </c>
       <c r="DK42" t="n">
-        <v>0.04568966724162626</v>
+        <v>4.20238306264873</v>
       </c>
       <c r="DO42" t="n">
-        <v>31.12128995061565</v>
+        <v>43.86086454995747</v>
       </c>
       <c r="EC42" t="n">
-        <v>141.3058583145359</v>
+        <v>805.5422994403893</v>
       </c>
       <c r="EF42" t="n">
-        <v>148.4864377582185</v>
+        <v>31.9483164320572</v>
       </c>
       <c r="EO42" t="n">
-        <v>6.986934797282764</v>
+        <v>19.03553691961389</v>
       </c>
       <c r="ER42" t="n">
-        <v>10.85835695508953</v>
+        <v>12.25380102467412</v>
       </c>
       <c r="HL42" t="n">
-        <v>36.7557350900975</v>
+        <v>24.2317220954754</v>
       </c>
       <c r="LA42" t="n">
-        <v>4.795118330667521</v>
+        <v>0.3704875864884571</v>
       </c>
     </row>
     <row r="43">
@@ -2980,52 +3108,55 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>642.3165497783436</v>
+        <v>682.4686996317905</v>
       </c>
       <c r="G43" t="n">
-        <v>586.5688173991879</v>
+        <v>323.2928489482044</v>
+      </c>
+      <c r="J43" t="n">
+        <v>18.35563827122238</v>
       </c>
       <c r="M43" t="n">
-        <v>67.24456258915075</v>
+        <v>97.39581800996075</v>
       </c>
       <c r="P43" t="n">
-        <v>37.46503411661427</v>
+        <v>78.53644036175135</v>
       </c>
       <c r="S43" t="n">
-        <v>63.37353393878384</v>
+        <v>75.78252839272758</v>
       </c>
       <c r="V43" t="n">
-        <v>43.21316002378883</v>
+        <v>45.24810050664498</v>
       </c>
       <c r="AH43" t="n">
-        <v>482.6760992035354</v>
+        <v>778.2270464880445</v>
       </c>
       <c r="AW43" t="n">
-        <v>15.95891697618524</v>
+        <v>10.88368835375945</v>
       </c>
       <c r="DK43" t="n">
-        <v>4.474920999375507</v>
+        <v>5.303967640396036</v>
       </c>
       <c r="DO43" t="n">
-        <v>98.25628526501198</v>
+        <v>52.35754980510252</v>
       </c>
       <c r="EC43" t="n">
-        <v>548.530470548586</v>
+        <v>271.2179036276047</v>
       </c>
       <c r="EF43" t="n">
-        <v>464.7197482847497</v>
+        <v>301.4305337046103</v>
       </c>
       <c r="EO43" t="n">
-        <v>4.169990310658422</v>
+        <v>13.09968474124938</v>
       </c>
       <c r="ER43" t="n">
-        <v>7.433651291025949</v>
+        <v>14.99554447745988</v>
       </c>
       <c r="HL43" t="n">
-        <v>58.42228173434341</v>
+        <v>33.54378744992365</v>
       </c>
       <c r="LA43" t="n">
-        <v>4.643674349866008</v>
+        <v>3.829776334551403</v>
       </c>
     </row>
     <row r="44">
@@ -3040,52 +3171,55 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2189.341829985095</v>
+        <v>116.1822605993518</v>
       </c>
       <c r="G44" t="n">
-        <v>686.9437991531821</v>
+        <v>753.741614407608</v>
+      </c>
+      <c r="J44" t="n">
+        <v>73.73135166934833</v>
       </c>
       <c r="M44" t="n">
-        <v>52.71235545019513</v>
+        <v>18.18624107859114</v>
       </c>
       <c r="P44" t="n">
-        <v>18.12653419861529</v>
+        <v>22.83105229519155</v>
       </c>
       <c r="S44" t="n">
-        <v>40.70438113055025</v>
+        <v>76.51891014497836</v>
       </c>
       <c r="V44" t="n">
-        <v>1.351151268660772</v>
+        <v>18.62840933113817</v>
       </c>
       <c r="AH44" t="n">
-        <v>309.6655931668699</v>
+        <v>144.1087292784105</v>
       </c>
       <c r="AW44" t="n">
-        <v>3.224955639397475</v>
+        <v>19.48742920539445</v>
       </c>
       <c r="DK44" t="n">
-        <v>8.612200246637807</v>
+        <v>6.03542421261907</v>
       </c>
       <c r="DO44" t="n">
-        <v>5.71175277315189</v>
+        <v>92.01242022930771</v>
       </c>
       <c r="EC44" t="n">
-        <v>995.0794131925709</v>
+        <v>315.1236709010769</v>
       </c>
       <c r="EF44" t="n">
-        <v>439.6127381990778</v>
+        <v>174.4079014000122</v>
       </c>
       <c r="EO44" t="n">
-        <v>9.825645685561749</v>
+        <v>5.327179042447352</v>
       </c>
       <c r="ER44" t="n">
-        <v>8.609762568836686</v>
+        <v>11.54396933154256</v>
       </c>
       <c r="HL44" t="n">
-        <v>64.45132970334441</v>
+        <v>55.80074518716002</v>
       </c>
       <c r="LA44" t="n">
-        <v>2.1216232974731</v>
+        <v>3.421144854161565</v>
       </c>
     </row>
     <row r="45">
@@ -3100,52 +3234,55 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1532.974707295748</v>
+        <v>1815.049327041904</v>
       </c>
       <c r="G45" t="n">
-        <v>629.6491249694334</v>
+        <v>639.1756868120908</v>
+      </c>
+      <c r="J45" t="n">
+        <v>77.01728157397612</v>
       </c>
       <c r="M45" t="n">
-        <v>89.49762440467435</v>
+        <v>49.29843051477408</v>
       </c>
       <c r="P45" t="n">
-        <v>34.92629646877491</v>
+        <v>77.53183406477592</v>
       </c>
       <c r="S45" t="n">
-        <v>86.08046723575626</v>
+        <v>17.29093413061751</v>
       </c>
       <c r="V45" t="n">
-        <v>6.368109456018233</v>
+        <v>32.00104688114439</v>
       </c>
       <c r="AH45" t="n">
-        <v>416.1382993867952</v>
+        <v>158.6649544072115</v>
       </c>
       <c r="AW45" t="n">
-        <v>7.128344947102503</v>
+        <v>18.48331131777424</v>
       </c>
       <c r="DK45" t="n">
-        <v>1.427122071326248</v>
+        <v>3.27470710655969</v>
       </c>
       <c r="DO45" t="n">
-        <v>12.76986061767044</v>
+        <v>13.09662992806528</v>
       </c>
       <c r="EC45" t="n">
-        <v>323.9676671979914</v>
+        <v>307.4568556269637</v>
       </c>
       <c r="EF45" t="n">
-        <v>308.9251308840481</v>
+        <v>277.3085092329085</v>
       </c>
       <c r="EO45" t="n">
-        <v>7.887834118848644</v>
+        <v>8.981067200045565</v>
       </c>
       <c r="ER45" t="n">
-        <v>8.19248552650744</v>
+        <v>12.73337318865019</v>
       </c>
       <c r="HL45" t="n">
-        <v>69.61975775090987</v>
+        <v>4.026292106344631</v>
       </c>
       <c r="LA45" t="n">
-        <v>2.574765951257495</v>
+        <v>0.9176132076107957</v>
       </c>
     </row>
     <row r="46">
@@ -3160,52 +3297,55 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1734.067446803838</v>
+        <v>1027.567746148952</v>
       </c>
       <c r="G46" t="n">
-        <v>172.943276185266</v>
+        <v>302.5185316573179</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11.42855826670787</v>
       </c>
       <c r="M46" t="n">
-        <v>44.06453341793095</v>
+        <v>21.72076635666064</v>
       </c>
       <c r="P46" t="n">
-        <v>19.21926676583592</v>
+        <v>14.8295737494096</v>
       </c>
       <c r="S46" t="n">
-        <v>70.90261583772464</v>
+        <v>55.97575035934448</v>
       </c>
       <c r="V46" t="n">
-        <v>34.17960775536921</v>
+        <v>28.11112367637726</v>
       </c>
       <c r="AH46" t="n">
-        <v>292.6877222684733</v>
+        <v>262.4060776648213</v>
       </c>
       <c r="AW46" t="n">
-        <v>18.96531018075754</v>
+        <v>17.80660109880366</v>
       </c>
       <c r="DK46" t="n">
-        <v>5.178070637193038</v>
+        <v>2.810654304948256</v>
       </c>
       <c r="DO46" t="n">
-        <v>97.35412191030989</v>
+        <v>9.920654343515366</v>
       </c>
       <c r="EC46" t="n">
-        <v>816.8843639883452</v>
+        <v>295.8330598990094</v>
       </c>
       <c r="EF46" t="n">
-        <v>314.798700700084</v>
+        <v>238.9328479439182</v>
       </c>
       <c r="EO46" t="n">
-        <v>4.05921399067897</v>
+        <v>18.3103774151701</v>
       </c>
       <c r="ER46" t="n">
-        <v>1.397064458570361</v>
+        <v>11.93828721604062</v>
       </c>
       <c r="HL46" t="n">
-        <v>34.57362156819242</v>
+        <v>66.63610349904212</v>
       </c>
       <c r="LA46" t="n">
-        <v>3.258346334849649</v>
+        <v>2.507053517747457</v>
       </c>
     </row>
     <row r="47">
@@ -3220,52 +3360,55 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>593.8307436032458</v>
+        <v>750.7324089419191</v>
       </c>
       <c r="G47" t="n">
-        <v>89.10799811343581</v>
+        <v>429.8026136131871</v>
+      </c>
+      <c r="J47" t="n">
+        <v>17.01355178054116</v>
       </c>
       <c r="M47" t="n">
-        <v>52.66890022987916</v>
+        <v>68.94214951199704</v>
       </c>
       <c r="P47" t="n">
-        <v>41.26829468990793</v>
+        <v>37.49080298915578</v>
       </c>
       <c r="S47" t="n">
-        <v>23.19906100788033</v>
+        <v>47.38526249906641</v>
       </c>
       <c r="V47" t="n">
-        <v>39.42601509870271</v>
+        <v>13.99635572791968</v>
       </c>
       <c r="AH47" t="n">
-        <v>518.0929742502698</v>
+        <v>456.4552838819249</v>
       </c>
       <c r="AW47" t="n">
-        <v>7.154307132556033</v>
+        <v>1.515039131928269</v>
       </c>
       <c r="DK47" t="n">
-        <v>5.675857010390554</v>
+        <v>8.225743682273288</v>
       </c>
       <c r="DO47" t="n">
-        <v>31.6855612997947</v>
+        <v>40.58479980764969</v>
       </c>
       <c r="EC47" t="n">
-        <v>87.13666039035972</v>
+        <v>177.0761606874548</v>
       </c>
       <c r="EF47" t="n">
-        <v>482.5885505296575</v>
+        <v>286.5703632881607</v>
       </c>
       <c r="EO47" t="n">
-        <v>19.87993133610258</v>
+        <v>18.0099026999025</v>
       </c>
       <c r="ER47" t="n">
-        <v>4.724686498270952</v>
+        <v>8.338155451291701</v>
       </c>
       <c r="HL47" t="n">
-        <v>84.88311752836327</v>
+        <v>41.19486451130548</v>
       </c>
       <c r="LA47" t="n">
-        <v>2.611215410339018</v>
+        <v>1.575403940671802</v>
       </c>
     </row>
     <row r="48">
@@ -3280,52 +3423,55 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>819.6925606223201</v>
+        <v>1066.187765605482</v>
       </c>
       <c r="G48" t="n">
-        <v>487.8997961267283</v>
+        <v>369.64231329468</v>
+      </c>
+      <c r="J48" t="n">
+        <v>24.57623548923755</v>
       </c>
       <c r="M48" t="n">
-        <v>37.64467334818305</v>
+        <v>43.34184592683891</v>
       </c>
       <c r="P48" t="n">
-        <v>74.4110438145851</v>
+        <v>62.24933598315404</v>
       </c>
       <c r="S48" t="n">
-        <v>25.65994089061392</v>
+        <v>86.15799541374646</v>
       </c>
       <c r="V48" t="n">
-        <v>17.20142721560479</v>
+        <v>11.61077390193972</v>
       </c>
       <c r="AH48" t="n">
-        <v>560.7816248744908</v>
+        <v>691.8676680287672</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.415766895324351</v>
+        <v>15.39433392361419</v>
       </c>
       <c r="DK48" t="n">
-        <v>7.968481151804713</v>
+        <v>7.640390925914746</v>
       </c>
       <c r="DO48" t="n">
-        <v>61.32641589623552</v>
+        <v>42.94615590842119</v>
       </c>
       <c r="EC48" t="n">
-        <v>389.6928553967498</v>
+        <v>744.1803293494285</v>
       </c>
       <c r="EF48" t="n">
-        <v>492.8031034162189</v>
+        <v>377.1447152633259</v>
       </c>
       <c r="EO48" t="n">
-        <v>6.916624591541276</v>
+        <v>4.72660827877291</v>
       </c>
       <c r="ER48" t="n">
-        <v>16.14338176904641</v>
+        <v>12.10103877451466</v>
       </c>
       <c r="HL48" t="n">
-        <v>90.65139237719603</v>
+        <v>78.65097550014754</v>
       </c>
       <c r="LA48" t="n">
-        <v>1.304604518127132</v>
+        <v>3.290570486680728</v>
       </c>
     </row>
     <row r="49">
@@ -3340,52 +3486,55 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2691.844552281078</v>
+        <v>329.3274519370846</v>
       </c>
       <c r="G49" t="n">
-        <v>532.5725542931391</v>
+        <v>723.9391198823895</v>
+      </c>
+      <c r="J49" t="n">
+        <v>78.624064173996</v>
       </c>
       <c r="M49" t="n">
-        <v>68.86453243126222</v>
+        <v>31.54095230817056</v>
       </c>
       <c r="P49" t="n">
-        <v>70.67737723729101</v>
+        <v>87.28294790562011</v>
       </c>
       <c r="S49" t="n">
-        <v>53.53423270070171</v>
+        <v>26.80347836051371</v>
       </c>
       <c r="V49" t="n">
-        <v>27.63367750895169</v>
+        <v>44.56315094902603</v>
       </c>
       <c r="AH49" t="n">
-        <v>971.8188052347375</v>
+        <v>334.3277505837018</v>
       </c>
       <c r="AW49" t="n">
-        <v>10.33221490339767</v>
+        <v>12.2775855579668</v>
       </c>
       <c r="DK49" t="n">
-        <v>8.527255746238124</v>
+        <v>0.03636200106373333</v>
       </c>
       <c r="DO49" t="n">
-        <v>89.52972257594998</v>
+        <v>36.06479128144861</v>
       </c>
       <c r="EC49" t="n">
-        <v>260.8866897872999</v>
+        <v>280.8938552942865</v>
       </c>
       <c r="EF49" t="n">
-        <v>72.81958779487624</v>
+        <v>354.6527572128737</v>
       </c>
       <c r="EO49" t="n">
-        <v>17.04546536682036</v>
+        <v>17.48180084439612</v>
       </c>
       <c r="ER49" t="n">
-        <v>6.104389626256916</v>
+        <v>1.254187413008379</v>
       </c>
       <c r="HL49" t="n">
-        <v>31.2680230578528</v>
+        <v>4.202184072750603</v>
       </c>
       <c r="LA49" t="n">
-        <v>1.508340212312432</v>
+        <v>0.5929729761754232</v>
       </c>
     </row>
     <row r="50">
@@ -3400,52 +3549,55 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2533.090881944584</v>
+        <v>2391.011784441186</v>
       </c>
       <c r="G50" t="n">
-        <v>410.0435014188242</v>
+        <v>430.1312821513998</v>
+      </c>
+      <c r="J50" t="n">
+        <v>77.50585019068524</v>
       </c>
       <c r="M50" t="n">
-        <v>95.78398383977448</v>
+        <v>53.28964442391831</v>
       </c>
       <c r="P50" t="n">
-        <v>3.584137735668325</v>
+        <v>98.98017851583046</v>
       </c>
       <c r="S50" t="n">
-        <v>27.29157117971022</v>
+        <v>24.73407335362935</v>
       </c>
       <c r="V50" t="n">
-        <v>48.62275810559396</v>
+        <v>19.53089201397703</v>
       </c>
       <c r="AH50" t="n">
-        <v>77.04478253035529</v>
+        <v>218.9666707301047</v>
       </c>
       <c r="AW50" t="n">
-        <v>3.827811295500745</v>
+        <v>19.51809241579412</v>
       </c>
       <c r="DK50" t="n">
-        <v>2.314263171886343</v>
+        <v>2.683531001398983</v>
       </c>
       <c r="DO50" t="n">
-        <v>59.00097926034529</v>
+        <v>22.08343415754091</v>
       </c>
       <c r="EC50" t="n">
-        <v>479.4831751809513</v>
+        <v>458.3858462505267</v>
       </c>
       <c r="EF50" t="n">
-        <v>186.2808556353149</v>
+        <v>259.8442259174676</v>
       </c>
       <c r="EO50" t="n">
-        <v>9.547487603336789</v>
+        <v>16.35078453782791</v>
       </c>
       <c r="ER50" t="n">
-        <v>15.61972589999447</v>
+        <v>13.46220279435224</v>
       </c>
       <c r="HL50" t="n">
-        <v>48.71251592970276</v>
+        <v>9.644733864714251</v>
       </c>
       <c r="LA50" t="n">
-        <v>4.92304273456596</v>
+        <v>0.9619207672704888</v>
       </c>
     </row>
     <row r="51">
@@ -3460,52 +3612,55 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>460.3868392684843</v>
+        <v>339.8886264545954</v>
       </c>
       <c r="G51" t="n">
-        <v>773.4577578619147</v>
+        <v>561.4649554725443</v>
+      </c>
+      <c r="J51" t="n">
+        <v>65.64036113040849</v>
       </c>
       <c r="M51" t="n">
-        <v>63.87894517527606</v>
+        <v>51.31561887905086</v>
       </c>
       <c r="P51" t="n">
-        <v>84.29422521334192</v>
+        <v>26.67220861251465</v>
       </c>
       <c r="S51" t="n">
-        <v>52.18570879914539</v>
+        <v>4.501424678336852</v>
       </c>
       <c r="V51" t="n">
-        <v>15.3054596944007</v>
+        <v>19.74514229354624</v>
       </c>
       <c r="AH51" t="n">
-        <v>358.7172399825108</v>
+        <v>498.7781587127043</v>
       </c>
       <c r="AW51" t="n">
-        <v>11.03953130702273</v>
+        <v>13.31076909875534</v>
       </c>
       <c r="DK51" t="n">
-        <v>2.050423813343727</v>
+        <v>7.172158605944094</v>
       </c>
       <c r="DO51" t="n">
-        <v>99.4039693495444</v>
+        <v>8.689360129823044</v>
       </c>
       <c r="EC51" t="n">
-        <v>58.92106087942006</v>
+        <v>967.0448504032302</v>
       </c>
       <c r="EF51" t="n">
-        <v>136.4986992910626</v>
+        <v>417.6865127581992</v>
       </c>
       <c r="EO51" t="n">
-        <v>16.80938149648635</v>
+        <v>12.95201433130538</v>
       </c>
       <c r="ER51" t="n">
-        <v>12.78927667164036</v>
+        <v>5.324552268709983</v>
       </c>
       <c r="HL51" t="n">
-        <v>23.01981675073845</v>
+        <v>97.47519841752344</v>
       </c>
       <c r="LA51" t="n">
-        <v>3.380100674633674</v>
+        <v>2.20834418809025</v>
       </c>
     </row>
     <row r="52">
@@ -3520,52 +3675,55 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1441.788646874057</v>
+        <v>2643.220590953884</v>
       </c>
       <c r="G52" t="n">
-        <v>127.1764488794571</v>
+        <v>701.0043210878674</v>
+      </c>
+      <c r="J52" t="n">
+        <v>6.776225109714606</v>
       </c>
       <c r="M52" t="n">
-        <v>64.7600792950382</v>
+        <v>32.74851749463907</v>
       </c>
       <c r="P52" t="n">
-        <v>2.710271448898482</v>
+        <v>82.56929880145691</v>
       </c>
       <c r="S52" t="n">
-        <v>18.9964784011963</v>
+        <v>66.46082870285893</v>
       </c>
       <c r="V52" t="n">
-        <v>47.38612924391958</v>
+        <v>11.56692084989963</v>
       </c>
       <c r="AH52" t="n">
-        <v>489.6548503401081</v>
+        <v>337.6887013052462</v>
       </c>
       <c r="AW52" t="n">
-        <v>8.026041690204623</v>
+        <v>8.686685379996572</v>
       </c>
       <c r="DK52" t="n">
-        <v>9.511307114120285</v>
+        <v>7.152080637294085</v>
       </c>
       <c r="DO52" t="n">
-        <v>32.77778761475493</v>
+        <v>73.65833844234987</v>
       </c>
       <c r="EC52" t="n">
-        <v>441.2652781171416</v>
+        <v>181.0717980729865</v>
       </c>
       <c r="EF52" t="n">
-        <v>367.1392417911339</v>
+        <v>232.0172411211562</v>
       </c>
       <c r="EO52" t="n">
-        <v>5.880171706925042</v>
+        <v>18.5442980214328</v>
       </c>
       <c r="ER52" t="n">
-        <v>7.678770348086854</v>
+        <v>16.64086735766996</v>
       </c>
       <c r="HL52" t="n">
-        <v>58.03276663788232</v>
+        <v>8.595454135377768</v>
       </c>
       <c r="LA52" t="n">
-        <v>1.012349120676795</v>
+        <v>1.419908133389176</v>
       </c>
     </row>
     <row r="53">
@@ -3580,52 +3738,55 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2219.793639040327</v>
+        <v>2558.644532902508</v>
       </c>
       <c r="G53" t="n">
-        <v>254.2680187695191</v>
+        <v>87.24226158043899</v>
+      </c>
+      <c r="J53" t="n">
+        <v>36.54998636010032</v>
       </c>
       <c r="M53" t="n">
-        <v>16.10527245579794</v>
+        <v>31.20974705136214</v>
       </c>
       <c r="P53" t="n">
-        <v>13.41093581406069</v>
+        <v>34.20756590770225</v>
       </c>
       <c r="S53" t="n">
-        <v>81.22696709154103</v>
+        <v>87.21254877453309</v>
       </c>
       <c r="V53" t="n">
-        <v>12.96371717155722</v>
+        <v>44.09025861787268</v>
       </c>
       <c r="AH53" t="n">
-        <v>206.585984397675</v>
+        <v>595.3143602528008</v>
       </c>
       <c r="AW53" t="n">
-        <v>15.54422827798551</v>
+        <v>0.2633700583934151</v>
       </c>
       <c r="DK53" t="n">
-        <v>8.282259011547344</v>
+        <v>7.929067610942403</v>
       </c>
       <c r="DO53" t="n">
-        <v>10.1643725102571</v>
+        <v>16.47083094139042</v>
       </c>
       <c r="EC53" t="n">
-        <v>659.172634569491</v>
+        <v>642.0593680947679</v>
       </c>
       <c r="EF53" t="n">
-        <v>93.30361427072998</v>
+        <v>191.1290441956767</v>
       </c>
       <c r="EO53" t="n">
-        <v>8.04022757825506</v>
+        <v>12.17241456227829</v>
       </c>
       <c r="ER53" t="n">
-        <v>17.9738029384946</v>
+        <v>5.18046926290155</v>
       </c>
       <c r="HL53" t="n">
-        <v>53.59324201853958</v>
+        <v>71.40763747391648</v>
       </c>
       <c r="LA53" t="n">
-        <v>0.4122368481767413</v>
+        <v>3.81674197847547</v>
       </c>
     </row>
     <row r="54">
@@ -3640,52 +3801,55 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1252.334898567245</v>
+        <v>914.6903663061393</v>
       </c>
       <c r="G54" t="n">
-        <v>510.9875264054471</v>
+        <v>626.1544034531522</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.312509611345295</v>
       </c>
       <c r="M54" t="n">
-        <v>37.8708926936101</v>
+        <v>32.0143738948264</v>
       </c>
       <c r="P54" t="n">
-        <v>54.19718643804661</v>
+        <v>51.72737299542882</v>
       </c>
       <c r="S54" t="n">
-        <v>85.86601014515036</v>
+        <v>70.55938158815862</v>
       </c>
       <c r="V54" t="n">
-        <v>21.4651597297016</v>
+        <v>33.24024648984859</v>
       </c>
       <c r="AH54" t="n">
-        <v>883.0854086552667</v>
+        <v>319.4955546308942</v>
       </c>
       <c r="AW54" t="n">
-        <v>14.53002948085414</v>
+        <v>8.679385064714726</v>
       </c>
       <c r="DK54" t="n">
-        <v>8.532607146836996</v>
+        <v>4.197930467869707</v>
       </c>
       <c r="DO54" t="n">
-        <v>71.01436442741708</v>
+        <v>90.6821911580106</v>
       </c>
       <c r="EC54" t="n">
-        <v>214.0743498920899</v>
+        <v>146.2417911963065</v>
       </c>
       <c r="EF54" t="n">
-        <v>111.0442414124795</v>
+        <v>205.7938876459878</v>
       </c>
       <c r="EO54" t="n">
-        <v>14.09200425527034</v>
+        <v>19.48971715418908</v>
       </c>
       <c r="ER54" t="n">
-        <v>2.191158287746753</v>
+        <v>12.71559628017145</v>
       </c>
       <c r="HL54" t="n">
-        <v>88.87771663121752</v>
+        <v>65.94189373924658</v>
       </c>
       <c r="LA54" t="n">
-        <v>1.474283707807821</v>
+        <v>0.8028765947221417</v>
       </c>
     </row>
     <row r="55">
@@ -3700,52 +3864,55 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>350.7816816633767</v>
+        <v>1519.221099669811</v>
       </c>
       <c r="G55" t="n">
-        <v>748.6656831537622</v>
+        <v>29.18337723563811</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.4582569202572939</v>
       </c>
       <c r="M55" t="n">
-        <v>6.479428292860268</v>
+        <v>25.79551341166923</v>
       </c>
       <c r="P55" t="n">
-        <v>89.49679807544926</v>
+        <v>6.213647077423657</v>
       </c>
       <c r="S55" t="n">
-        <v>7.938886168393122</v>
+        <v>85.00238753836379</v>
       </c>
       <c r="V55" t="n">
-        <v>19.55457729944221</v>
+        <v>8.689503299775513</v>
       </c>
       <c r="AH55" t="n">
-        <v>196.9570760658498</v>
+        <v>366.4595923763351</v>
       </c>
       <c r="AW55" t="n">
-        <v>19.63936843495104</v>
+        <v>7.637800208265739</v>
       </c>
       <c r="DK55" t="n">
-        <v>2.924091168289421</v>
+        <v>8.968024786460582</v>
       </c>
       <c r="DO55" t="n">
-        <v>30.10033743360121</v>
+        <v>9.998442292425636</v>
       </c>
       <c r="EC55" t="n">
-        <v>972.4015870581298</v>
+        <v>650.0860175877475</v>
       </c>
       <c r="EF55" t="n">
-        <v>181.1796732161956</v>
+        <v>163.6483734432523</v>
       </c>
       <c r="EO55" t="n">
-        <v>17.653470408781</v>
+        <v>8.980753477232355</v>
       </c>
       <c r="ER55" t="n">
-        <v>0.657701840564473</v>
+        <v>0.5964594010098256</v>
       </c>
       <c r="HL55" t="n">
-        <v>93.94593539988199</v>
+        <v>58.89539098948305</v>
       </c>
       <c r="LA55" t="n">
-        <v>3.306842236251083</v>
+        <v>4.94230719147294</v>
       </c>
     </row>
     <row r="56">
@@ -3760,52 +3927,55 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2074.381708176572</v>
+        <v>2398.503582086766</v>
       </c>
       <c r="G56" t="n">
-        <v>381.592958417605</v>
+        <v>342.3286602860643</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.52949529181888</v>
       </c>
       <c r="M56" t="n">
-        <v>21.62997083135815</v>
+        <v>16.31708105857861</v>
       </c>
       <c r="P56" t="n">
-        <v>43.3735813038973</v>
+        <v>70.19437139306622</v>
       </c>
       <c r="S56" t="n">
-        <v>72.87085909885268</v>
+        <v>26.73982123721321</v>
       </c>
       <c r="V56" t="n">
-        <v>7.91200327100583</v>
+        <v>35.85809343119477</v>
       </c>
       <c r="AH56" t="n">
-        <v>426.6032573542429</v>
+        <v>321.4545658745803</v>
       </c>
       <c r="AW56" t="n">
-        <v>19.09073640553256</v>
+        <v>17.78656696801175</v>
       </c>
       <c r="DK56" t="n">
-        <v>7.204021860583234</v>
+        <v>1.399006139309107</v>
       </c>
       <c r="DO56" t="n">
-        <v>4.977687494651639</v>
+        <v>10.42356948370971</v>
       </c>
       <c r="EC56" t="n">
-        <v>971.3896043023606</v>
+        <v>275.6564503289711</v>
       </c>
       <c r="EF56" t="n">
-        <v>311.7946359202355</v>
+        <v>126.7777418034469</v>
       </c>
       <c r="EO56" t="n">
-        <v>3.98814702658546</v>
+        <v>11.12924183078983</v>
       </c>
       <c r="ER56" t="n">
-        <v>18.70199436491188</v>
+        <v>14.59256161719384</v>
       </c>
       <c r="HL56" t="n">
-        <v>30.07179842050196</v>
+        <v>81.14518474636618</v>
       </c>
       <c r="LA56" t="n">
-        <v>1.955039198624516</v>
+        <v>2.399398493863728</v>
       </c>
     </row>
     <row r="57">
@@ -3820,52 +3990,55 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>807.4806141234816</v>
+        <v>407.2219511240522</v>
       </c>
       <c r="G57" t="n">
-        <v>524.904554721898</v>
+        <v>428.7520456885767</v>
+      </c>
+      <c r="J57" t="n">
+        <v>19.76834300811536</v>
       </c>
       <c r="M57" t="n">
-        <v>69.11329211952896</v>
+        <v>41.59953327568431</v>
       </c>
       <c r="P57" t="n">
-        <v>0.7726318082471373</v>
+        <v>63.38407138903614</v>
       </c>
       <c r="S57" t="n">
-        <v>6.38299683890301</v>
+        <v>71.72788414321474</v>
       </c>
       <c r="V57" t="n">
-        <v>9.65090099638104</v>
+        <v>41.48359617355923</v>
       </c>
       <c r="AH57" t="n">
-        <v>726.992814068455</v>
+        <v>590.4401657491693</v>
       </c>
       <c r="AW57" t="n">
-        <v>13.79678681112523</v>
+        <v>13.69940790795881</v>
       </c>
       <c r="DK57" t="n">
-        <v>6.979368827362725</v>
+        <v>0.2957935627982755</v>
       </c>
       <c r="DO57" t="n">
-        <v>3.967898449660678</v>
+        <v>26.09563668754985</v>
       </c>
       <c r="EC57" t="n">
-        <v>928.0596806310485</v>
+        <v>754.9908784116103</v>
       </c>
       <c r="EF57" t="n">
-        <v>336.5747265652488</v>
+        <v>236.9019432484144</v>
       </c>
       <c r="EO57" t="n">
-        <v>15.72974392777792</v>
+        <v>10.34336055448496</v>
       </c>
       <c r="ER57" t="n">
-        <v>14.33099489402475</v>
+        <v>11.20762645074618</v>
       </c>
       <c r="HL57" t="n">
-        <v>52.1902530153491</v>
+        <v>38.71961020913224</v>
       </c>
       <c r="LA57" t="n">
-        <v>3.029465707332034</v>
+        <v>4.840947715530649</v>
       </c>
     </row>
     <row r="58">
@@ -3880,52 +4053,55 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>207.8902907274485</v>
+        <v>1833.111520084988</v>
       </c>
       <c r="G58" t="n">
-        <v>40.51522200876985</v>
+        <v>375.4376853722991</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.1212589442521339</v>
       </c>
       <c r="M58" t="n">
-        <v>84.75161063630379</v>
+        <v>76.13214473972734</v>
       </c>
       <c r="P58" t="n">
-        <v>20.66897453628306</v>
+        <v>40.97413393700722</v>
       </c>
       <c r="S58" t="n">
-        <v>15.37231550835621</v>
+        <v>47.21802780933986</v>
       </c>
       <c r="V58" t="n">
-        <v>40.81057757910193</v>
+        <v>29.51713984981999</v>
       </c>
       <c r="AH58" t="n">
-        <v>421.0730087925084</v>
+        <v>188.6166121470254</v>
       </c>
       <c r="AW58" t="n">
-        <v>16.76429918175594</v>
+        <v>5.671691466014737</v>
       </c>
       <c r="DK58" t="n">
-        <v>6.124516300074205</v>
+        <v>0.681985488844884</v>
       </c>
       <c r="DO58" t="n">
-        <v>57.03491292775593</v>
+        <v>67.72111513362916</v>
       </c>
       <c r="EC58" t="n">
-        <v>244.0751406370316</v>
+        <v>698.0407291063131</v>
       </c>
       <c r="EF58" t="n">
-        <v>234.5197964051028</v>
+        <v>312.4818646131062</v>
       </c>
       <c r="EO58" t="n">
-        <v>14.59117489666234</v>
+        <v>14.68678553960636</v>
       </c>
       <c r="ER58" t="n">
-        <v>5.464626066128444</v>
+        <v>1.725286999387625</v>
       </c>
       <c r="HL58" t="n">
-        <v>93.05582776106746</v>
+        <v>66.47499577829892</v>
       </c>
       <c r="LA58" t="n">
-        <v>4.857859268581163</v>
+        <v>2.295159809721193</v>
       </c>
     </row>
     <row r="59">
@@ -3940,52 +4116,55 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1778.519945895133</v>
+        <v>206.7478949325389</v>
       </c>
       <c r="G59" t="n">
-        <v>362.6207739193046</v>
+        <v>198.6451238087826</v>
+      </c>
+      <c r="J59" t="n">
+        <v>61.09750193851221</v>
       </c>
       <c r="M59" t="n">
-        <v>67.6803893452163</v>
+        <v>56.72925440988897</v>
       </c>
       <c r="P59" t="n">
-        <v>2.237126506205767</v>
+        <v>5.25318254667334</v>
       </c>
       <c r="S59" t="n">
-        <v>71.14976436795622</v>
+        <v>3.044818743068345</v>
       </c>
       <c r="V59" t="n">
-        <v>8.72665858699172</v>
+        <v>38.39774585530539</v>
       </c>
       <c r="AH59" t="n">
-        <v>900.4458465106095</v>
+        <v>931.963524486094</v>
       </c>
       <c r="AW59" t="n">
-        <v>5.20611644730546</v>
+        <v>17.0994559540451</v>
       </c>
       <c r="DK59" t="n">
-        <v>2.654400689954932</v>
+        <v>7.67413714568818</v>
       </c>
       <c r="DO59" t="n">
-        <v>17.98707919116353</v>
+        <v>60.62757810972163</v>
       </c>
       <c r="EC59" t="n">
-        <v>566.1094903851856</v>
+        <v>748.6746783587428</v>
       </c>
       <c r="EF59" t="n">
-        <v>259.0114717292884</v>
+        <v>440.9560395142909</v>
       </c>
       <c r="EO59" t="n">
-        <v>17.12662930568149</v>
+        <v>15.50433074637562</v>
       </c>
       <c r="ER59" t="n">
-        <v>18.36420771522068</v>
+        <v>8.299513834016601</v>
       </c>
       <c r="HL59" t="n">
-        <v>63.9011772262851</v>
+        <v>15.40815984114093</v>
       </c>
       <c r="LA59" t="n">
-        <v>0.999507790113433</v>
+        <v>1.930424544712758</v>
       </c>
     </row>
     <row r="60">
@@ -4000,52 +4179,55 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1171.072592525045</v>
+        <v>84.97025294983051</v>
       </c>
       <c r="G60" t="n">
-        <v>284.4184828840793</v>
+        <v>386.7958033419119</v>
+      </c>
+      <c r="J60" t="n">
+        <v>76.20739715490716</v>
       </c>
       <c r="M60" t="n">
-        <v>75.5863087324191</v>
+        <v>79.60762139074507</v>
       </c>
       <c r="P60" t="n">
-        <v>60.86202578976921</v>
+        <v>88.34785459926393</v>
       </c>
       <c r="S60" t="n">
-        <v>39.77888510978293</v>
+        <v>74.5255967338488</v>
       </c>
       <c r="V60" t="n">
-        <v>48.13975011832154</v>
+        <v>37.72171090058457</v>
       </c>
       <c r="AH60" t="n">
-        <v>924.2977610486657</v>
+        <v>79.69582354189653</v>
       </c>
       <c r="AW60" t="n">
-        <v>19.46599682522577</v>
+        <v>7.683026441281122</v>
       </c>
       <c r="DK60" t="n">
-        <v>1.62692871056991</v>
+        <v>5.406635845072949</v>
       </c>
       <c r="DO60" t="n">
-        <v>64.31475862950413</v>
+        <v>3.921139441343424</v>
       </c>
       <c r="EC60" t="n">
-        <v>191.8794094665821</v>
+        <v>239.9125368408522</v>
       </c>
       <c r="EF60" t="n">
-        <v>73.95662796245645</v>
+        <v>257.4136751147607</v>
       </c>
       <c r="EO60" t="n">
-        <v>10.5586191404613</v>
+        <v>7.914608001776557</v>
       </c>
       <c r="ER60" t="n">
-        <v>12.65198959293688</v>
+        <v>10.81468591814373</v>
       </c>
       <c r="HL60" t="n">
-        <v>75.99587819062459</v>
+        <v>93.62192625339904</v>
       </c>
       <c r="LA60" t="n">
-        <v>0.1045573751791273</v>
+        <v>1.707680841252663</v>
       </c>
     </row>
     <row r="61">
@@ -4060,52 +4242,55 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2313.462325301352</v>
+        <v>1791.277960424927</v>
       </c>
       <c r="G61" t="n">
-        <v>63.35696921431548</v>
+        <v>619.5721075540583</v>
+      </c>
+      <c r="J61" t="n">
+        <v>19.56049072084965</v>
       </c>
       <c r="M61" t="n">
-        <v>25.10201069127682</v>
+        <v>96.94305886568395</v>
       </c>
       <c r="P61" t="n">
-        <v>13.43017354302205</v>
+        <v>96.05202427635179</v>
       </c>
       <c r="S61" t="n">
-        <v>14.84546139434476</v>
+        <v>20.36128492443126</v>
       </c>
       <c r="V61" t="n">
-        <v>23.71123031945608</v>
+        <v>12.45527575314285</v>
       </c>
       <c r="AH61" t="n">
-        <v>480.922317576925</v>
+        <v>451.7607100513992</v>
       </c>
       <c r="AW61" t="n">
-        <v>16.23645755604231</v>
+        <v>11.81936127182697</v>
       </c>
       <c r="DK61" t="n">
-        <v>1.243161395422836</v>
+        <v>0.9838093673534354</v>
       </c>
       <c r="DO61" t="n">
-        <v>75.3251015774397</v>
+        <v>47.91575393761593</v>
       </c>
       <c r="EC61" t="n">
-        <v>258.0642986330142</v>
+        <v>548.468392861504</v>
       </c>
       <c r="EF61" t="n">
-        <v>197.8054595128846</v>
+        <v>303.5260573728914</v>
       </c>
       <c r="EO61" t="n">
-        <v>12.76600883688348</v>
+        <v>14.85741116212622</v>
       </c>
       <c r="ER61" t="n">
-        <v>10.87300663202213</v>
+        <v>1.344746736084901</v>
       </c>
       <c r="HL61" t="n">
-        <v>86.21996592868946</v>
+        <v>11.01676341663735</v>
       </c>
       <c r="LA61" t="n">
-        <v>2.761585370772379</v>
+        <v>3.604332191697996</v>
       </c>
     </row>
     <row r="62">
@@ -4120,52 +4305,55 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>491.1756684883987</v>
+        <v>1653.845714994317</v>
       </c>
       <c r="G62" t="n">
-        <v>623.64364261497</v>
+        <v>546.6832455514256</v>
+      </c>
+      <c r="J62" t="n">
+        <v>85.07085885212715</v>
       </c>
       <c r="M62" t="n">
-        <v>68.83550093519767</v>
+        <v>26.84674836229299</v>
       </c>
       <c r="P62" t="n">
-        <v>44.86846452689435</v>
+        <v>51.40588406607301</v>
       </c>
       <c r="S62" t="n">
-        <v>9.247990917456306</v>
+        <v>43.46282127732329</v>
       </c>
       <c r="V62" t="n">
-        <v>29.16752407445039</v>
+        <v>23.73668874685461</v>
       </c>
       <c r="AH62" t="n">
-        <v>342.623035996963</v>
+        <v>215.5112594930053</v>
       </c>
       <c r="AW62" t="n">
-        <v>14.95687571197223</v>
+        <v>2.287341159762759</v>
       </c>
       <c r="DK62" t="n">
-        <v>3.062077849493403</v>
+        <v>3.145060689776811</v>
       </c>
       <c r="DO62" t="n">
-        <v>24.64324237004316</v>
+        <v>99.31787980790439</v>
       </c>
       <c r="EC62" t="n">
-        <v>129.645208654935</v>
+        <v>967.440724732357</v>
       </c>
       <c r="EF62" t="n">
-        <v>268.4309222739696</v>
+        <v>409.5567609751259</v>
       </c>
       <c r="EO62" t="n">
-        <v>19.05793705108641</v>
+        <v>2.31694009263901</v>
       </c>
       <c r="ER62" t="n">
-        <v>4.166861041759664</v>
+        <v>19.65306574851293</v>
       </c>
       <c r="HL62" t="n">
-        <v>33.94313554463726</v>
+        <v>57.94074265999504</v>
       </c>
       <c r="LA62" t="n">
-        <v>1.966018510236032</v>
+        <v>3.804453737200366</v>
       </c>
     </row>
     <row r="63">
@@ -4180,52 +4368,55 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1925.550917425898</v>
+        <v>991.809893475277</v>
       </c>
       <c r="G63" t="n">
-        <v>563.4536317844685</v>
+        <v>592.5507201582034</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1930926679080791</v>
       </c>
       <c r="M63" t="n">
-        <v>34.40777826516602</v>
+        <v>1.955145454338914</v>
       </c>
       <c r="P63" t="n">
-        <v>96.75450976632497</v>
+        <v>55.14334579809142</v>
       </c>
       <c r="S63" t="n">
-        <v>47.45660693236613</v>
+        <v>53.39186274433785</v>
       </c>
       <c r="V63" t="n">
-        <v>36.4017026901467</v>
+        <v>17.2623967496896</v>
       </c>
       <c r="AH63" t="n">
-        <v>723.5365086729755</v>
+        <v>414.7677639957126</v>
       </c>
       <c r="AW63" t="n">
-        <v>6.808585658929811</v>
+        <v>16.31416016610716</v>
       </c>
       <c r="DK63" t="n">
-        <v>4.191098513854304</v>
+        <v>2.603892390068774</v>
       </c>
       <c r="DO63" t="n">
-        <v>54.56984824296467</v>
+        <v>89.49008397006482</v>
       </c>
       <c r="EC63" t="n">
-        <v>99.57315431765612</v>
+        <v>443.0596103337315</v>
       </c>
       <c r="EF63" t="n">
-        <v>224.7403148476946</v>
+        <v>490.6451949148855</v>
       </c>
       <c r="EO63" t="n">
-        <v>3.048003500756535</v>
+        <v>4.732730635572489</v>
       </c>
       <c r="ER63" t="n">
-        <v>11.99913048523508</v>
+        <v>19.59653852404175</v>
       </c>
       <c r="HL63" t="n">
-        <v>34.50336166158448</v>
+        <v>57.43700633460507</v>
       </c>
       <c r="LA63" t="n">
-        <v>0.2766873423460481</v>
+        <v>2.945502467266127</v>
       </c>
     </row>
     <row r="64">
@@ -4240,52 +4431,55 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>580.9224106780825</v>
+        <v>2361.115363154693</v>
       </c>
       <c r="G64" t="n">
-        <v>717.0538434234428</v>
+        <v>446.5507625555392</v>
+      </c>
+      <c r="J64" t="n">
+        <v>77.4017167410818</v>
       </c>
       <c r="M64" t="n">
-        <v>37.5678187558791</v>
+        <v>10.32741981888051</v>
       </c>
       <c r="P64" t="n">
-        <v>12.70052582813157</v>
+        <v>81.57693125831689</v>
       </c>
       <c r="S64" t="n">
-        <v>58.6503575885327</v>
+        <v>1.126544545697361</v>
       </c>
       <c r="V64" t="n">
-        <v>49.49226673571305</v>
+        <v>31.66694447978254</v>
       </c>
       <c r="AH64" t="n">
-        <v>108.428536036519</v>
+        <v>406.6373628424716</v>
       </c>
       <c r="AW64" t="n">
-        <v>2.705926979707187</v>
+        <v>11.09783550279604</v>
       </c>
       <c r="DK64" t="n">
-        <v>0.4833017913146276</v>
+        <v>0.2933349561752996</v>
       </c>
       <c r="DO64" t="n">
-        <v>12.26979906045551</v>
+        <v>56.89600217810652</v>
       </c>
       <c r="EC64" t="n">
-        <v>548.341789326244</v>
+        <v>59.46342865687981</v>
       </c>
       <c r="EF64" t="n">
-        <v>361.5843473605124</v>
+        <v>211.0812371890782</v>
       </c>
       <c r="EO64" t="n">
-        <v>1.599307749321779</v>
+        <v>3.752673174875161</v>
       </c>
       <c r="ER64" t="n">
-        <v>6.560953340605151</v>
+        <v>17.97123173198521</v>
       </c>
       <c r="HL64" t="n">
-        <v>39.86295169653076</v>
+        <v>54.29063408036402</v>
       </c>
       <c r="LA64" t="n">
-        <v>3.199718762934535</v>
+        <v>1.903186884549463</v>
       </c>
     </row>
     <row r="65">
@@ -4300,52 +4494,55 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2451.307130772893</v>
+        <v>138.6320911352332</v>
       </c>
       <c r="G65" t="n">
-        <v>311.9602267873217</v>
+        <v>431.7988499136417</v>
+      </c>
+      <c r="J65" t="n">
+        <v>54.2716290620076</v>
       </c>
       <c r="M65" t="n">
-        <v>39.57796188760219</v>
+        <v>67.96968570436933</v>
       </c>
       <c r="P65" t="n">
-        <v>33.28746684542625</v>
+        <v>81.0714890114065</v>
       </c>
       <c r="S65" t="n">
-        <v>95.42382868755432</v>
+        <v>95.4923137170567</v>
       </c>
       <c r="V65" t="n">
-        <v>44.13486523990953</v>
+        <v>10.90411262277996</v>
       </c>
       <c r="AH65" t="n">
-        <v>512.1069394598705</v>
+        <v>40.98141377956965</v>
       </c>
       <c r="AW65" t="n">
-        <v>18.64755206951035</v>
+        <v>6.576455008820814</v>
       </c>
       <c r="DK65" t="n">
-        <v>4.83134668360397</v>
+        <v>9.499359092163697</v>
       </c>
       <c r="DO65" t="n">
-        <v>33.26178424388703</v>
+        <v>91.16077128715658</v>
       </c>
       <c r="EC65" t="n">
-        <v>230.0580585162132</v>
+        <v>610.8889809525576</v>
       </c>
       <c r="EF65" t="n">
-        <v>205.3437549347348</v>
+        <v>410.96022228088</v>
       </c>
       <c r="EO65" t="n">
-        <v>15.2257640721437</v>
+        <v>1.594263417517845</v>
       </c>
       <c r="ER65" t="n">
-        <v>19.28157443950023</v>
+        <v>5.667733706674039</v>
       </c>
       <c r="HL65" t="n">
-        <v>89.04177686216457</v>
+        <v>78.82142253313962</v>
       </c>
       <c r="LA65" t="n">
-        <v>3.772679574768126</v>
+        <v>1.717213543451889</v>
       </c>
     </row>
     <row r="66">
@@ -4360,52 +4557,55 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2940.30944664492</v>
+        <v>2852.600790170079</v>
       </c>
       <c r="G66" t="n">
-        <v>441.7298427062967</v>
+        <v>414.169950931846</v>
+      </c>
+      <c r="J66" t="n">
+        <v>19.82678796753656</v>
       </c>
       <c r="M66" t="n">
-        <v>64.04263407954637</v>
+        <v>60.90424472477358</v>
       </c>
       <c r="P66" t="n">
-        <v>48.74294299628671</v>
+        <v>23.84301733426402</v>
       </c>
       <c r="S66" t="n">
-        <v>67.70444346645435</v>
+        <v>7.579164966856943</v>
       </c>
       <c r="V66" t="n">
-        <v>30.90380155147556</v>
+        <v>21.42930791149814</v>
       </c>
       <c r="AH66" t="n">
-        <v>752.3702379287107</v>
+        <v>960.6806579586613</v>
       </c>
       <c r="AW66" t="n">
-        <v>16.2490521910647</v>
+        <v>11.3193431810791</v>
       </c>
       <c r="DK66" t="n">
-        <v>2.699337893478257</v>
+        <v>4.157449268969717</v>
       </c>
       <c r="DO66" t="n">
-        <v>76.43329502817541</v>
+        <v>66.76291301360547</v>
       </c>
       <c r="EC66" t="n">
-        <v>687.4816342155657</v>
+        <v>637.8926090860515</v>
       </c>
       <c r="EF66" t="n">
-        <v>112.1068641848005</v>
+        <v>136.6123526723008</v>
       </c>
       <c r="EO66" t="n">
-        <v>13.57698992537576</v>
+        <v>13.65927310088117</v>
       </c>
       <c r="ER66" t="n">
-        <v>0.8059045367300777</v>
+        <v>19.05112944884668</v>
       </c>
       <c r="HL66" t="n">
-        <v>44.75721104926992</v>
+        <v>74.53228451234514</v>
       </c>
       <c r="LA66" t="n">
-        <v>0.02153747716918675</v>
+        <v>0.8573444681179615</v>
       </c>
     </row>
     <row r="67">
@@ -4420,52 +4620,55 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>739.764318494682</v>
+        <v>1432.390883347667</v>
       </c>
       <c r="G67" t="n">
-        <v>191.9681916261439</v>
+        <v>389.0310613265183</v>
+      </c>
+      <c r="J67" t="n">
+        <v>60.84997498656615</v>
       </c>
       <c r="M67" t="n">
-        <v>77.05143899908965</v>
+        <v>33.20488740772561</v>
       </c>
       <c r="P67" t="n">
-        <v>17.0101782557958</v>
+        <v>65.52233347320184</v>
       </c>
       <c r="S67" t="n">
-        <v>72.16253854944171</v>
+        <v>65.03522291310642</v>
       </c>
       <c r="V67" t="n">
-        <v>9.532369908660964</v>
+        <v>32.52117364375984</v>
       </c>
       <c r="AH67" t="n">
-        <v>765.6153850613944</v>
+        <v>809.015566438418</v>
       </c>
       <c r="AW67" t="n">
-        <v>14.95567365501339</v>
+        <v>8.355355851075135</v>
       </c>
       <c r="DK67" t="n">
-        <v>0.3521236238664704</v>
+        <v>4.062849191904661</v>
       </c>
       <c r="DO67" t="n">
-        <v>12.95890178018692</v>
+        <v>55.31893601717472</v>
       </c>
       <c r="EC67" t="n">
-        <v>357.3312647616861</v>
+        <v>278.5296016143299</v>
       </c>
       <c r="EF67" t="n">
-        <v>83.87521240117157</v>
+        <v>100.148720909234</v>
       </c>
       <c r="EO67" t="n">
-        <v>0.6007121416843608</v>
+        <v>17.64664357869552</v>
       </c>
       <c r="ER67" t="n">
-        <v>9.991263091026745</v>
+        <v>3.940158159886331</v>
       </c>
       <c r="HL67" t="n">
-        <v>48.71357072217474</v>
+        <v>95.71776428183439</v>
       </c>
       <c r="LA67" t="n">
-        <v>4.095245572263122</v>
+        <v>3.694218684538147</v>
       </c>
     </row>
     <row r="68">
@@ -4480,52 +4683,55 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2984.776094533163</v>
+        <v>2060.795106084175</v>
       </c>
       <c r="G68" t="n">
-        <v>279.9580621341486</v>
+        <v>726.7021676176706</v>
+      </c>
+      <c r="J68" t="n">
+        <v>76.66796426259599</v>
       </c>
       <c r="M68" t="n">
-        <v>69.30885090647439</v>
+        <v>66.18385043860128</v>
       </c>
       <c r="P68" t="n">
-        <v>7.560664751404323</v>
+        <v>41.31950626395206</v>
       </c>
       <c r="S68" t="n">
-        <v>89.32746872335949</v>
+        <v>57.83218859502398</v>
       </c>
       <c r="V68" t="n">
-        <v>44.8952472257803</v>
+        <v>46.81033105409411</v>
       </c>
       <c r="AH68" t="n">
-        <v>276.761809383354</v>
+        <v>513.6000548553407</v>
       </c>
       <c r="AW68" t="n">
-        <v>3.847985496368942</v>
+        <v>18.30446634952335</v>
       </c>
       <c r="DK68" t="n">
-        <v>9.298279748510746</v>
+        <v>6.562237346593262</v>
       </c>
       <c r="DO68" t="n">
-        <v>63.13849081946765</v>
+        <v>36.43050133778398</v>
       </c>
       <c r="EC68" t="n">
-        <v>727.2355033376261</v>
+        <v>917.2893280695791</v>
       </c>
       <c r="EF68" t="n">
-        <v>143.5232603199802</v>
+        <v>134.8717387879065</v>
       </c>
       <c r="EO68" t="n">
-        <v>8.614166504829264</v>
+        <v>11.30436809767255</v>
       </c>
       <c r="ER68" t="n">
-        <v>10.12069759127741</v>
+        <v>9.457523595816683</v>
       </c>
       <c r="HL68" t="n">
-        <v>33.93952827048356</v>
+        <v>7.748936927574235</v>
       </c>
       <c r="LA68" t="n">
-        <v>0.3385900494801813</v>
+        <v>2.234826906781127</v>
       </c>
     </row>
     <row r="69">
@@ -4540,52 +4746,55 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2149.006827460783</v>
+        <v>858.2121200918345</v>
       </c>
       <c r="G69" t="n">
-        <v>791.607765873624</v>
+        <v>131.3901621375973</v>
+      </c>
+      <c r="J69" t="n">
+        <v>33.82571574702882</v>
       </c>
       <c r="M69" t="n">
-        <v>13.83418690390384</v>
+        <v>61.16746860454317</v>
       </c>
       <c r="P69" t="n">
-        <v>86.6191737381951</v>
+        <v>11.20215646864677</v>
       </c>
       <c r="S69" t="n">
-        <v>4.370686354099973</v>
+        <v>98.29161599910265</v>
       </c>
       <c r="V69" t="n">
-        <v>3.204452563981441</v>
+        <v>47.0072931392351</v>
       </c>
       <c r="AH69" t="n">
-        <v>972.5037922545037</v>
+        <v>348.6691999672309</v>
       </c>
       <c r="AW69" t="n">
-        <v>6.157432510163909</v>
+        <v>10.12604148853965</v>
       </c>
       <c r="DK69" t="n">
-        <v>7.215008490121891</v>
+        <v>7.933593449780437</v>
       </c>
       <c r="DO69" t="n">
-        <v>51.95203114467056</v>
+        <v>2.689342598347821</v>
       </c>
       <c r="EC69" t="n">
-        <v>713.2351753790956</v>
+        <v>923.248025335542</v>
       </c>
       <c r="EF69" t="n">
-        <v>405.2163753669084</v>
+        <v>66.72435033743534</v>
       </c>
       <c r="EO69" t="n">
-        <v>4.353159828796698</v>
+        <v>16.0986809530457</v>
       </c>
       <c r="ER69" t="n">
-        <v>12.35631585359885</v>
+        <v>14.22019283485833</v>
       </c>
       <c r="HL69" t="n">
-        <v>12.41598876236092</v>
+        <v>39.06671835559639</v>
       </c>
       <c r="LA69" t="n">
-        <v>0.3740813853658992</v>
+        <v>0.3693347973493027</v>
       </c>
     </row>
     <row r="70">
@@ -4600,52 +4809,55 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2336.604580407204</v>
+        <v>1109.042370099896</v>
       </c>
       <c r="G70" t="n">
-        <v>194.1209263949425</v>
+        <v>679.3608673604232</v>
+      </c>
+      <c r="J70" t="n">
+        <v>62.408997990514</v>
       </c>
       <c r="M70" t="n">
-        <v>56.37217107159397</v>
+        <v>81.22007660910069</v>
       </c>
       <c r="P70" t="n">
-        <v>66.23542093956979</v>
+        <v>71.24165187114667</v>
       </c>
       <c r="S70" t="n">
-        <v>76.90908837438849</v>
+        <v>33.45257411594053</v>
       </c>
       <c r="V70" t="n">
-        <v>44.08573734399161</v>
+        <v>9.125460413861003</v>
       </c>
       <c r="AH70" t="n">
-        <v>18.17053341293695</v>
+        <v>113.4247434281386</v>
       </c>
       <c r="AW70" t="n">
-        <v>13.6296321597917</v>
+        <v>19.96628949924941</v>
       </c>
       <c r="DK70" t="n">
-        <v>9.852109390146815</v>
+        <v>4.398231319702944</v>
       </c>
       <c r="DO70" t="n">
-        <v>6.797549184129892</v>
+        <v>1.537708696219831</v>
       </c>
       <c r="EC70" t="n">
-        <v>885.9411703073617</v>
+        <v>360.5766815775607</v>
       </c>
       <c r="EF70" t="n">
-        <v>105.7417644067857</v>
+        <v>415.6065852599782</v>
       </c>
       <c r="EO70" t="n">
-        <v>16.10915008441698</v>
+        <v>19.66031308773329</v>
       </c>
       <c r="ER70" t="n">
-        <v>19.61441540585379</v>
+        <v>10.4157774865576</v>
       </c>
       <c r="HL70" t="n">
-        <v>89.54057286724621</v>
+        <v>34.96208340969448</v>
       </c>
       <c r="LA70" t="n">
-        <v>4.430618705154333</v>
+        <v>1.867942840974892</v>
       </c>
     </row>
     <row r="71">
@@ -4660,52 +4872,55 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>723.8017311831563</v>
+        <v>1048.344375708974</v>
       </c>
       <c r="G71" t="n">
-        <v>752.3430977118072</v>
+        <v>236.4650310308492</v>
+      </c>
+      <c r="J71" t="n">
+        <v>91.0534295175211</v>
       </c>
       <c r="M71" t="n">
-        <v>73.18281856651193</v>
+        <v>52.23605628829745</v>
       </c>
       <c r="P71" t="n">
-        <v>30.4900217390371</v>
+        <v>14.4124767620705</v>
       </c>
       <c r="S71" t="n">
-        <v>96.23764563733414</v>
+        <v>28.00841143940165</v>
       </c>
       <c r="V71" t="n">
-        <v>39.57734532753776</v>
+        <v>48.07008752404973</v>
       </c>
       <c r="AH71" t="n">
-        <v>449.3931188244306</v>
+        <v>180.0030357782322</v>
       </c>
       <c r="AW71" t="n">
-        <v>5.785319380736233</v>
+        <v>9.445669870217175</v>
       </c>
       <c r="DK71" t="n">
-        <v>7.381921373619066</v>
+        <v>9.576215800664883</v>
       </c>
       <c r="DO71" t="n">
-        <v>97.37905955242371</v>
+        <v>16.23027656828052</v>
       </c>
       <c r="EC71" t="n">
-        <v>496.3967670155718</v>
+        <v>382.9638605344837</v>
       </c>
       <c r="EF71" t="n">
-        <v>246.7745088314681</v>
+        <v>80.20278669005054</v>
       </c>
       <c r="EO71" t="n">
-        <v>7.53335951056952</v>
+        <v>2.347414325549211</v>
       </c>
       <c r="ER71" t="n">
-        <v>2.443527370257197</v>
+        <v>19.95336080515415</v>
       </c>
       <c r="HL71" t="n">
-        <v>38.60837739964145</v>
+        <v>39.08888898009513</v>
       </c>
       <c r="LA71" t="n">
-        <v>4.56582111448422</v>
+        <v>4.77883084964674</v>
       </c>
     </row>
     <row r="72">
@@ -4720,52 +4935,55 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>487.9844463824213</v>
+        <v>363.5094906559907</v>
       </c>
       <c r="G72" t="n">
-        <v>56.79640866361675</v>
+        <v>99.47574205422444</v>
+      </c>
+      <c r="J72" t="n">
+        <v>60.05534350311714</v>
       </c>
       <c r="M72" t="n">
-        <v>49.40685710531295</v>
+        <v>96.96175953475566</v>
       </c>
       <c r="P72" t="n">
-        <v>11.81754220614483</v>
+        <v>63.419454930844</v>
       </c>
       <c r="S72" t="n">
-        <v>14.77383322084784</v>
+        <v>65.13833485333174</v>
       </c>
       <c r="V72" t="n">
-        <v>49.01520896007369</v>
+        <v>8.908876211676187</v>
       </c>
       <c r="AH72" t="n">
-        <v>95.06409481600076</v>
+        <v>315.5147656515581</v>
       </c>
       <c r="AW72" t="n">
-        <v>11.8188503949151</v>
+        <v>1.658454119008976</v>
       </c>
       <c r="DK72" t="n">
-        <v>8.691706504711751</v>
+        <v>7.270058434864056</v>
       </c>
       <c r="DO72" t="n">
-        <v>76.62554419904217</v>
+        <v>46.37766570925507</v>
       </c>
       <c r="EC72" t="n">
-        <v>259.7514106099977</v>
+        <v>807.9349306213895</v>
       </c>
       <c r="EF72" t="n">
-        <v>240.5713799188624</v>
+        <v>129.234391989303</v>
       </c>
       <c r="EO72" t="n">
-        <v>2.247920716767189</v>
+        <v>7.399706836786222</v>
       </c>
       <c r="ER72" t="n">
-        <v>14.26139954767336</v>
+        <v>12.02289785746536</v>
       </c>
       <c r="HL72" t="n">
-        <v>95.49034173747974</v>
+        <v>78.7368634331706</v>
       </c>
       <c r="LA72" t="n">
-        <v>0.1857024064933499</v>
+        <v>0.4417924862481309</v>
       </c>
     </row>
     <row r="73">
@@ -4780,52 +4998,55 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1353.582081520875</v>
+        <v>972.4143203694728</v>
       </c>
       <c r="G73" t="n">
-        <v>440.1141547899666</v>
+        <v>601.1061222947552</v>
+      </c>
+      <c r="J73" t="n">
+        <v>46.59132833565867</v>
       </c>
       <c r="M73" t="n">
-        <v>36.38284081025218</v>
+        <v>37.01659774092128</v>
       </c>
       <c r="P73" t="n">
-        <v>97.42265117868992</v>
+        <v>43.61665909901752</v>
       </c>
       <c r="S73" t="n">
-        <v>16.09961878458036</v>
+        <v>93.49490060805041</v>
       </c>
       <c r="V73" t="n">
-        <v>46.27714307069625</v>
+        <v>25.2218970583915</v>
       </c>
       <c r="AH73" t="n">
-        <v>532.242104978426</v>
+        <v>80.32622193277183</v>
       </c>
       <c r="AW73" t="n">
-        <v>9.020165886203628</v>
+        <v>3.89499741785682</v>
       </c>
       <c r="DK73" t="n">
-        <v>3.046323631314408</v>
+        <v>4.696246839376819</v>
       </c>
       <c r="DO73" t="n">
-        <v>5.234195453231283</v>
+        <v>56.48131596753176</v>
       </c>
       <c r="EC73" t="n">
-        <v>76.70303658560462</v>
+        <v>739.475924029393</v>
       </c>
       <c r="EF73" t="n">
-        <v>451.9411522474944</v>
+        <v>400.7780010060636</v>
       </c>
       <c r="EO73" t="n">
-        <v>18.06261840947764</v>
+        <v>11.59879579121774</v>
       </c>
       <c r="ER73" t="n">
-        <v>9.76209687469234</v>
+        <v>12.11965266014795</v>
       </c>
       <c r="HL73" t="n">
-        <v>65.3963507057923</v>
+        <v>16.03438143081112</v>
       </c>
       <c r="LA73" t="n">
-        <v>1.850848712962513</v>
+        <v>2.364133031950723</v>
       </c>
     </row>
     <row r="74">
@@ -4840,52 +5061,55 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1455.483727295288</v>
+        <v>1608.913576912854</v>
       </c>
       <c r="G74" t="n">
-        <v>525.5708206942448</v>
+        <v>293.5766591271668</v>
+      </c>
+      <c r="J74" t="n">
+        <v>83.05977507643925</v>
       </c>
       <c r="M74" t="n">
-        <v>51.37118163017627</v>
+        <v>92.3485527129304</v>
       </c>
       <c r="P74" t="n">
-        <v>42.49499654325191</v>
+        <v>47.73070663432362</v>
       </c>
       <c r="S74" t="n">
-        <v>31.36984608472477</v>
+        <v>44.95479612163482</v>
       </c>
       <c r="V74" t="n">
-        <v>21.58536704037894</v>
+        <v>39.24333773733471</v>
       </c>
       <c r="AH74" t="n">
-        <v>383.0918053949861</v>
+        <v>505.2857724651961</v>
       </c>
       <c r="AW74" t="n">
-        <v>4.919056584657959</v>
+        <v>5.161499234039031</v>
       </c>
       <c r="DK74" t="n">
-        <v>4.970291982409588</v>
+        <v>7.234047455452694</v>
       </c>
       <c r="DO74" t="n">
-        <v>8.4813266788893</v>
+        <v>65.73893745946775</v>
       </c>
       <c r="EC74" t="n">
-        <v>42.60421751015176</v>
+        <v>988.552746546769</v>
       </c>
       <c r="EF74" t="n">
-        <v>387.8940728393392</v>
+        <v>181.8814191488076</v>
       </c>
       <c r="EO74" t="n">
-        <v>2.753959190999209</v>
+        <v>5.749049931169092</v>
       </c>
       <c r="ER74" t="n">
-        <v>3.560986925700556</v>
+        <v>9.99819747820964</v>
       </c>
       <c r="HL74" t="n">
-        <v>98.16704689989092</v>
+        <v>19.63951084808079</v>
       </c>
       <c r="LA74" t="n">
-        <v>3.921027271960357</v>
+        <v>4.923293623330486</v>
       </c>
     </row>
     <row r="75">
@@ -4900,52 +5124,55 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1193.888127265366</v>
+        <v>1211.151349006692</v>
       </c>
       <c r="G75" t="n">
-        <v>380.7024152516175</v>
+        <v>392.3609157148678</v>
+      </c>
+      <c r="J75" t="n">
+        <v>70.46644091759372</v>
       </c>
       <c r="M75" t="n">
-        <v>72.18412175691658</v>
+        <v>82.15778285065105</v>
       </c>
       <c r="P75" t="n">
-        <v>49.11637779312702</v>
+        <v>99.26065744515485</v>
       </c>
       <c r="S75" t="n">
-        <v>67.51805621388193</v>
+        <v>33.87080009730696</v>
       </c>
       <c r="V75" t="n">
-        <v>9.472773221747421</v>
+        <v>11.21363875692563</v>
       </c>
       <c r="AH75" t="n">
-        <v>102.4159602155947</v>
+        <v>105.7254096971109</v>
       </c>
       <c r="AW75" t="n">
-        <v>18.59659426471148</v>
+        <v>0.6059455630176802</v>
       </c>
       <c r="DK75" t="n">
-        <v>8.764343799042276</v>
+        <v>5.820042604537385</v>
       </c>
       <c r="DO75" t="n">
-        <v>91.44376991679576</v>
+        <v>44.1518284223464</v>
       </c>
       <c r="EC75" t="n">
-        <v>502.8030058378336</v>
+        <v>961.3126206423983</v>
       </c>
       <c r="EF75" t="n">
-        <v>25.94801910685857</v>
+        <v>56.42327985740997</v>
       </c>
       <c r="EO75" t="n">
-        <v>4.143113382597639</v>
+        <v>19.67934969956702</v>
       </c>
       <c r="ER75" t="n">
-        <v>4.201598305617091</v>
+        <v>17.61680426140387</v>
       </c>
       <c r="HL75" t="n">
-        <v>6.338479266371144</v>
+        <v>93.93268118420175</v>
       </c>
       <c r="LA75" t="n">
-        <v>2.07899871118894</v>
+        <v>3.593190935553583</v>
       </c>
     </row>
     <row r="76">
@@ -4960,52 +5187,55 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>553.6009006851158</v>
+        <v>2623.21075229614</v>
       </c>
       <c r="G76" t="n">
-        <v>210.3930142488047</v>
+        <v>671.0345689924266</v>
+      </c>
+      <c r="J76" t="n">
+        <v>28.82113412119847</v>
       </c>
       <c r="M76" t="n">
-        <v>72.66025945364269</v>
+        <v>0.006878563988399478</v>
       </c>
       <c r="P76" t="n">
-        <v>71.52841682120568</v>
+        <v>60.0573211500678</v>
       </c>
       <c r="S76" t="n">
-        <v>22.46877008578815</v>
+        <v>7.973192533252726</v>
       </c>
       <c r="V76" t="n">
-        <v>48.16624709502818</v>
+        <v>22.34098465233054</v>
       </c>
       <c r="AH76" t="n">
-        <v>410.8414069630379</v>
+        <v>938.6090276070078</v>
       </c>
       <c r="AW76" t="n">
-        <v>5.472406592749457</v>
+        <v>0.7410973204639193</v>
       </c>
       <c r="DK76" t="n">
-        <v>0.1117230168105254</v>
+        <v>4.818270233037402</v>
       </c>
       <c r="DO76" t="n">
-        <v>8.032167994881023</v>
+        <v>24.8809837332666</v>
       </c>
       <c r="EC76" t="n">
-        <v>726.6827735126489</v>
+        <v>128.2933048720696</v>
       </c>
       <c r="EF76" t="n">
-        <v>7.021373291621503</v>
+        <v>47.00442579806152</v>
       </c>
       <c r="EO76" t="n">
-        <v>17.36294152107832</v>
+        <v>10.12531090533575</v>
       </c>
       <c r="ER76" t="n">
-        <v>11.12251009972095</v>
+        <v>5.83876950238797</v>
       </c>
       <c r="HL76" t="n">
-        <v>46.01106844575899</v>
+        <v>90.05805432230657</v>
       </c>
       <c r="LA76" t="n">
-        <v>3.186090237654347</v>
+        <v>4.396678637266088</v>
       </c>
     </row>
     <row r="77">
@@ -5020,52 +5250,55 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>279.085376594079</v>
+        <v>2825.281491324557</v>
       </c>
       <c r="G77" t="n">
-        <v>630.9460605731132</v>
+        <v>558.316728285345</v>
+      </c>
+      <c r="J77" t="n">
+        <v>5.935186774376366</v>
       </c>
       <c r="M77" t="n">
-        <v>14.56875851441254</v>
+        <v>43.95407732787531</v>
       </c>
       <c r="P77" t="n">
-        <v>68.52598230606574</v>
+        <v>80.79777411306894</v>
       </c>
       <c r="S77" t="n">
-        <v>96.29992875970545</v>
+        <v>58.89428411426641</v>
       </c>
       <c r="V77" t="n">
-        <v>4.671577070317912</v>
+        <v>42.04800496253539</v>
       </c>
       <c r="AH77" t="n">
-        <v>502.2426103771658</v>
+        <v>860.9212686073948</v>
       </c>
       <c r="AW77" t="n">
-        <v>7.879685062662992</v>
+        <v>3.00082900705462</v>
       </c>
       <c r="DK77" t="n">
-        <v>3.804132338707755</v>
+        <v>1.40396587381533</v>
       </c>
       <c r="DO77" t="n">
-        <v>42.39073031680455</v>
+        <v>63.01938764586061</v>
       </c>
       <c r="EC77" t="n">
-        <v>66.94373546811438</v>
+        <v>436.3288947070744</v>
       </c>
       <c r="EF77" t="n">
-        <v>345.4366621344492</v>
+        <v>472.8872410085642</v>
       </c>
       <c r="EO77" t="n">
-        <v>17.65150216745719</v>
+        <v>11.31907360060205</v>
       </c>
       <c r="ER77" t="n">
-        <v>18.45955662507668</v>
+        <v>8.575834543902054</v>
       </c>
       <c r="HL77" t="n">
-        <v>10.89686550198855</v>
+        <v>65.78328318646382</v>
       </c>
       <c r="LA77" t="n">
-        <v>4.582965408299025</v>
+        <v>0.6772408793030865</v>
       </c>
     </row>
     <row r="78">
@@ -5080,52 +5313,55 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1881.286210796868</v>
+        <v>2931.176720833103</v>
       </c>
       <c r="G78" t="n">
-        <v>759.5723179769396</v>
+        <v>116.8402163326903</v>
+      </c>
+      <c r="J78" t="n">
+        <v>79.1182001724008</v>
       </c>
       <c r="M78" t="n">
-        <v>86.08520133627421</v>
+        <v>89.04612327795435</v>
       </c>
       <c r="P78" t="n">
-        <v>73.38821974132976</v>
+        <v>68.90878548110486</v>
       </c>
       <c r="S78" t="n">
-        <v>35.31792801797506</v>
+        <v>52.87656668891552</v>
       </c>
       <c r="V78" t="n">
-        <v>43.41668614197631</v>
+        <v>35.63969159302159</v>
       </c>
       <c r="AH78" t="n">
-        <v>702.5048136524745</v>
+        <v>4.463409251557748</v>
       </c>
       <c r="AW78" t="n">
-        <v>3.587152919142425</v>
+        <v>4.157867081840754</v>
       </c>
       <c r="DK78" t="n">
-        <v>9.140440304233252</v>
+        <v>7.608867473594973</v>
       </c>
       <c r="DO78" t="n">
-        <v>5.210591415056054</v>
+        <v>66.0033622624449</v>
       </c>
       <c r="EC78" t="n">
-        <v>593.222553274428</v>
+        <v>110.4106537983027</v>
       </c>
       <c r="EF78" t="n">
-        <v>192.4415588241306</v>
+        <v>128.4542139951517</v>
       </c>
       <c r="EO78" t="n">
-        <v>15.8461112351991</v>
+        <v>15.54230460821312</v>
       </c>
       <c r="ER78" t="n">
-        <v>5.357010904698589</v>
+        <v>13.92814359123555</v>
       </c>
       <c r="HL78" t="n">
-        <v>63.90906299343724</v>
+        <v>42.34693410696075</v>
       </c>
       <c r="LA78" t="n">
-        <v>0.2503437830200811</v>
+        <v>3.374905081008087</v>
       </c>
     </row>
     <row r="79">
@@ -5140,52 +5376,55 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2943.674712750802</v>
+        <v>2041.930767049982</v>
       </c>
       <c r="G79" t="n">
-        <v>280.3560073491271</v>
+        <v>284.5998138239078</v>
+      </c>
+      <c r="J79" t="n">
+        <v>31.37277283326434</v>
       </c>
       <c r="M79" t="n">
-        <v>6.066953649909612</v>
+        <v>63.28697065709699</v>
       </c>
       <c r="P79" t="n">
-        <v>67.07229919489043</v>
+        <v>14.56066945808755</v>
       </c>
       <c r="S79" t="n">
-        <v>82.6982495579603</v>
+        <v>40.84525733579004</v>
       </c>
       <c r="V79" t="n">
-        <v>31.6495088242512</v>
+        <v>4.157007903395393</v>
       </c>
       <c r="AH79" t="n">
-        <v>856.1635667313161</v>
+        <v>263.7218162159507</v>
       </c>
       <c r="AW79" t="n">
-        <v>5.790269734785102</v>
+        <v>19.52576164617503</v>
       </c>
       <c r="DK79" t="n">
-        <v>6.150536396542071</v>
+        <v>0.1443713327549401</v>
       </c>
       <c r="DO79" t="n">
-        <v>58.26504988750874</v>
+        <v>52.90944254057793</v>
       </c>
       <c r="EC79" t="n">
-        <v>122.453706176145</v>
+        <v>201.546995279974</v>
       </c>
       <c r="EF79" t="n">
-        <v>241.7863533618526</v>
+        <v>320.9580634346628</v>
       </c>
       <c r="EO79" t="n">
-        <v>14.91689200751768</v>
+        <v>4.447797426166662</v>
       </c>
       <c r="ER79" t="n">
-        <v>2.865265164163311</v>
+        <v>4.465265131538949</v>
       </c>
       <c r="HL79" t="n">
-        <v>15.80116567257791</v>
+        <v>1.637603779785313</v>
       </c>
       <c r="LA79" t="n">
-        <v>2.525066434759063</v>
+        <v>4.42355372054138</v>
       </c>
     </row>
     <row r="80">
@@ -5200,52 +5439,55 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1760.52811982138</v>
+        <v>1248.81953670299</v>
       </c>
       <c r="G80" t="n">
-        <v>561.3555282617928</v>
+        <v>261.8685793580618</v>
+      </c>
+      <c r="J80" t="n">
+        <v>92.7889732121496</v>
       </c>
       <c r="M80" t="n">
-        <v>53.90881675106316</v>
+        <v>41.87266263914707</v>
       </c>
       <c r="P80" t="n">
-        <v>60.72575590653381</v>
+        <v>70.4623468703608</v>
       </c>
       <c r="S80" t="n">
-        <v>38.50823738774351</v>
+        <v>83.32427278766663</v>
       </c>
       <c r="V80" t="n">
-        <v>9.604605827432389</v>
+        <v>42.15276049343439</v>
       </c>
       <c r="AH80" t="n">
-        <v>317.7412811667937</v>
+        <v>210.306087633678</v>
       </c>
       <c r="AW80" t="n">
-        <v>3.680540479570269</v>
+        <v>12.03753157519897</v>
       </c>
       <c r="DK80" t="n">
-        <v>0.7537423526925091</v>
+        <v>9.098089555388789</v>
       </c>
       <c r="DO80" t="n">
-        <v>47.60414610209281</v>
+        <v>78.67211406986492</v>
       </c>
       <c r="EC80" t="n">
-        <v>878.4234687385082</v>
+        <v>926.569572389161</v>
       </c>
       <c r="EF80" t="n">
-        <v>41.50149776273454</v>
+        <v>262.197383997323</v>
       </c>
       <c r="EO80" t="n">
-        <v>18.83912922118721</v>
+        <v>13.92769486598117</v>
       </c>
       <c r="ER80" t="n">
-        <v>17.92498422775368</v>
+        <v>4.75020368155918</v>
       </c>
       <c r="HL80" t="n">
-        <v>41.2857730126878</v>
+        <v>20.49329736448841</v>
       </c>
       <c r="LA80" t="n">
-        <v>0.7281869865914647</v>
+        <v>3.006756408887081</v>
       </c>
     </row>
     <row r="81">
@@ -5260,52 +5502,55 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1362.695164810835</v>
+        <v>2889.055327842006</v>
       </c>
       <c r="G81" t="n">
-        <v>109.1391675005775</v>
+        <v>68.75422126885749</v>
+      </c>
+      <c r="J81" t="n">
+        <v>85.65538226672106</v>
       </c>
       <c r="M81" t="n">
-        <v>51.54998997353214</v>
+        <v>1.10507384519194</v>
       </c>
       <c r="P81" t="n">
-        <v>68.63126289069122</v>
+        <v>51.78811311861159</v>
       </c>
       <c r="S81" t="n">
-        <v>57.47149360293101</v>
+        <v>0.09797731598967241</v>
       </c>
       <c r="V81" t="n">
-        <v>26.65280255569795</v>
+        <v>48.02826242899527</v>
       </c>
       <c r="AH81" t="n">
-        <v>795.5697343638934</v>
+        <v>906.6074649980641</v>
       </c>
       <c r="AW81" t="n">
-        <v>13.61120830102736</v>
+        <v>1.615105165168571</v>
       </c>
       <c r="DK81" t="n">
-        <v>9.869724486697594</v>
+        <v>1.562898822524093</v>
       </c>
       <c r="DO81" t="n">
-        <v>85.51071524620255</v>
+        <v>51.23408597561058</v>
       </c>
       <c r="EC81" t="n">
-        <v>149.2832335639831</v>
+        <v>392.2015034112562</v>
       </c>
       <c r="EF81" t="n">
-        <v>255.9521008710438</v>
+        <v>176.2453077705351</v>
       </c>
       <c r="EO81" t="n">
-        <v>18.97261583523626</v>
+        <v>10.15145039318396</v>
       </c>
       <c r="ER81" t="n">
-        <v>2.726701505656246</v>
+        <v>17.58559267348924</v>
       </c>
       <c r="HL81" t="n">
-        <v>74.28601022117411</v>
+        <v>29.35864784637211</v>
       </c>
       <c r="LA81" t="n">
-        <v>0.5365476723939494</v>
+        <v>2.518565182758632</v>
       </c>
     </row>
     <row r="82">
@@ -5320,52 +5565,55 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2247.878330022553</v>
+        <v>666.9344940586623</v>
       </c>
       <c r="G82" t="n">
-        <v>777.7761608528011</v>
+        <v>422.3645326766882</v>
+      </c>
+      <c r="J82" t="n">
+        <v>91.22924518900953</v>
       </c>
       <c r="M82" t="n">
-        <v>8.348754955231129</v>
+        <v>24.10619511979825</v>
       </c>
       <c r="P82" t="n">
-        <v>42.15857464847653</v>
+        <v>69.32751470358099</v>
       </c>
       <c r="S82" t="n">
-        <v>96.1067344700454</v>
+        <v>47.70848881752169</v>
       </c>
       <c r="V82" t="n">
-        <v>15.88483288868334</v>
+        <v>49.88433502132175</v>
       </c>
       <c r="AH82" t="n">
-        <v>531.674518677316</v>
+        <v>830.0324331697116</v>
       </c>
       <c r="AW82" t="n">
-        <v>11.30922907981727</v>
+        <v>5.307150961912173</v>
       </c>
       <c r="DK82" t="n">
-        <v>7.561281896101679</v>
+        <v>7.758946828920395</v>
       </c>
       <c r="DO82" t="n">
-        <v>88.79385370440738</v>
+        <v>95.5143001343411</v>
       </c>
       <c r="EC82" t="n">
-        <v>214.4348589120629</v>
+        <v>599.3216495747675</v>
       </c>
       <c r="EF82" t="n">
-        <v>315.0102571331208</v>
+        <v>264.8432193775112</v>
       </c>
       <c r="EO82" t="n">
-        <v>8.044443414596451</v>
+        <v>19.8456880362549</v>
       </c>
       <c r="ER82" t="n">
-        <v>12.33090207497974</v>
+        <v>12.3968453815116</v>
       </c>
       <c r="HL82" t="n">
-        <v>14.64449080207214</v>
+        <v>66.49041728068845</v>
       </c>
       <c r="LA82" t="n">
-        <v>4.001034863833263</v>
+        <v>2.595455686291695</v>
       </c>
     </row>
     <row r="83">
@@ -5380,52 +5628,55 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>319.9938841818029</v>
+        <v>597.8626802496251</v>
       </c>
       <c r="G83" t="n">
-        <v>537.114289600735</v>
+        <v>69.42865148085131</v>
+      </c>
+      <c r="J83" t="n">
+        <v>37.21027014886688</v>
       </c>
       <c r="M83" t="n">
-        <v>57.45657321143578</v>
+        <v>58.57973687057898</v>
       </c>
       <c r="P83" t="n">
-        <v>19.56082357434182</v>
+        <v>56.36267086460138</v>
       </c>
       <c r="S83" t="n">
-        <v>38.57893334781983</v>
+        <v>14.60865724365955</v>
       </c>
       <c r="V83" t="n">
-        <v>34.33687581279418</v>
+        <v>21.66020285359366</v>
       </c>
       <c r="AH83" t="n">
-        <v>331.9130105271819</v>
+        <v>253.1070817938175</v>
       </c>
       <c r="AW83" t="n">
-        <v>11.54710100362023</v>
+        <v>10.74576904035816</v>
       </c>
       <c r="DK83" t="n">
-        <v>5.436301855118141</v>
+        <v>1.737140112830632</v>
       </c>
       <c r="DO83" t="n">
-        <v>62.48739004658405</v>
+        <v>3.829820759944302</v>
       </c>
       <c r="EC83" t="n">
-        <v>608.291762716878</v>
+        <v>406.9058719913616</v>
       </c>
       <c r="EF83" t="n">
-        <v>9.779949897354701</v>
+        <v>402.097661710351</v>
       </c>
       <c r="EO83" t="n">
-        <v>15.58449577700552</v>
+        <v>6.175609768425472</v>
       </c>
       <c r="ER83" t="n">
-        <v>18.79392878194491</v>
+        <v>19.7748010728165</v>
       </c>
       <c r="HL83" t="n">
-        <v>73.30246165096528</v>
+        <v>59.0306799675031</v>
       </c>
       <c r="LA83" t="n">
-        <v>2.757917943587465</v>
+        <v>1.099424765171639</v>
       </c>
     </row>
     <row r="84">
@@ -5440,52 +5691,55 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>380.9535144185429</v>
+        <v>2833.510911128745</v>
       </c>
       <c r="G84" t="n">
-        <v>94.9030003041929</v>
+        <v>464.6464833533765</v>
+      </c>
+      <c r="J84" t="n">
+        <v>33.16376322353018</v>
       </c>
       <c r="M84" t="n">
-        <v>44.20885268159949</v>
+        <v>23.44265363375822</v>
       </c>
       <c r="P84" t="n">
-        <v>22.10987173636664</v>
+        <v>82.09725773183567</v>
       </c>
       <c r="S84" t="n">
-        <v>98.94862403880421</v>
+        <v>59.65240078855712</v>
       </c>
       <c r="V84" t="n">
-        <v>49.79277088065952</v>
+        <v>30.13728726169821</v>
       </c>
       <c r="AH84" t="n">
-        <v>521.1914400687117</v>
+        <v>649.4152170008505</v>
       </c>
       <c r="AW84" t="n">
-        <v>16.24927205623256</v>
+        <v>2.415925282725684</v>
       </c>
       <c r="DK84" t="n">
-        <v>5.363331306629222</v>
+        <v>5.856425235033633</v>
       </c>
       <c r="DO84" t="n">
-        <v>77.2486107685009</v>
+        <v>33.8963737603037</v>
       </c>
       <c r="EC84" t="n">
-        <v>199.9431137315253</v>
+        <v>924.6814370424192</v>
       </c>
       <c r="EF84" t="n">
-        <v>160.4460115639328</v>
+        <v>56.43931461151735</v>
       </c>
       <c r="EO84" t="n">
-        <v>19.55560683833372</v>
+        <v>12.26028685677342</v>
       </c>
       <c r="ER84" t="n">
-        <v>0.5283589937168998</v>
+        <v>16.32985197525774</v>
       </c>
       <c r="HL84" t="n">
-        <v>8.31364443034518</v>
+        <v>17.33997479754681</v>
       </c>
       <c r="LA84" t="n">
-        <v>3.100464280325013</v>
+        <v>3.588925848011444</v>
       </c>
     </row>
     <row r="85">
@@ -5500,52 +5754,55 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>440.3537116743773</v>
+        <v>936.5170421994228</v>
       </c>
       <c r="G85" t="n">
-        <v>206.077689425784</v>
+        <v>44.48310185689177</v>
+      </c>
+      <c r="J85" t="n">
+        <v>88.8726742542474</v>
       </c>
       <c r="M85" t="n">
-        <v>16.08518802786054</v>
+        <v>54.45003165260596</v>
       </c>
       <c r="P85" t="n">
-        <v>8.368095848145574</v>
+        <v>90.60607172085342</v>
       </c>
       <c r="S85" t="n">
-        <v>72.63232831543189</v>
+        <v>63.75993034881133</v>
       </c>
       <c r="V85" t="n">
-        <v>34.51240810040216</v>
+        <v>40.06934894075341</v>
       </c>
       <c r="AH85" t="n">
-        <v>902.840369438168</v>
+        <v>276.465535711015</v>
       </c>
       <c r="AW85" t="n">
-        <v>6.765861071455655</v>
+        <v>7.416518051892751</v>
       </c>
       <c r="DK85" t="n">
-        <v>6.317665976662247</v>
+        <v>0.6649173638980033</v>
       </c>
       <c r="DO85" t="n">
-        <v>95.53705910998715</v>
+        <v>58.77266910406311</v>
       </c>
       <c r="EC85" t="n">
-        <v>337.910904433642</v>
+        <v>193.6879736162263</v>
       </c>
       <c r="EF85" t="n">
-        <v>370.1838230380554</v>
+        <v>115.8628544909355</v>
       </c>
       <c r="EO85" t="n">
-        <v>5.514346095680462</v>
+        <v>5.296743020633901</v>
       </c>
       <c r="ER85" t="n">
-        <v>15.41670888757756</v>
+        <v>2.143100827914917</v>
       </c>
       <c r="HL85" t="n">
-        <v>7.481913289159858</v>
+        <v>65.42023140218632</v>
       </c>
       <c r="LA85" t="n">
-        <v>0.8003467008555537</v>
+        <v>1.039834175282812</v>
       </c>
     </row>
     <row r="86">
@@ -5560,52 +5817,55 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>435.165447652822</v>
+        <v>1877.315664091512</v>
       </c>
       <c r="G86" t="n">
-        <v>41.35209032196698</v>
+        <v>99.74672724709039</v>
+      </c>
+      <c r="J86" t="n">
+        <v>67.66388510620422</v>
       </c>
       <c r="M86" t="n">
-        <v>98.92502165146087</v>
+        <v>5.791280753433703</v>
       </c>
       <c r="P86" t="n">
-        <v>25.5940271093217</v>
+        <v>27.31816364123709</v>
       </c>
       <c r="S86" t="n">
-        <v>58.4638879272316</v>
+        <v>74.00146688093012</v>
       </c>
       <c r="V86" t="n">
-        <v>42.17834912550568</v>
+        <v>34.61126778481018</v>
       </c>
       <c r="AH86" t="n">
-        <v>428.245712119774</v>
+        <v>378.4050414058509</v>
       </c>
       <c r="AW86" t="n">
-        <v>10.8227396389133</v>
+        <v>3.677232536465278</v>
       </c>
       <c r="DK86" t="n">
-        <v>9.076027223989213</v>
+        <v>3.386809510094989</v>
       </c>
       <c r="DO86" t="n">
-        <v>34.59970689573507</v>
+        <v>21.85249970160045</v>
       </c>
       <c r="EC86" t="n">
-        <v>236.1791488114744</v>
+        <v>569.8505013782084</v>
       </c>
       <c r="EF86" t="n">
-        <v>104.0081987919327</v>
+        <v>113.2025148477284</v>
       </c>
       <c r="EO86" t="n">
-        <v>4.040929022219935</v>
+        <v>5.645423291543226</v>
       </c>
       <c r="ER86" t="n">
-        <v>3.063150765487228</v>
+        <v>5.313379028000307</v>
       </c>
       <c r="HL86" t="n">
-        <v>22.95812126742888</v>
+        <v>15.09233975389159</v>
       </c>
       <c r="LA86" t="n">
-        <v>1.102590148366183</v>
+        <v>3.908898520766591</v>
       </c>
     </row>
     <row r="87">
@@ -5620,52 +5880,55 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2980.225548827137</v>
+        <v>924.9048440474866</v>
       </c>
       <c r="G87" t="n">
-        <v>584.6566328842459</v>
+        <v>408.8460967061649</v>
+      </c>
+      <c r="J87" t="n">
+        <v>89.50352259340313</v>
       </c>
       <c r="M87" t="n">
-        <v>66.02640220262315</v>
+        <v>81.03139707598986</v>
       </c>
       <c r="P87" t="n">
-        <v>46.83630962160939</v>
+        <v>11.22327104349176</v>
       </c>
       <c r="S87" t="n">
-        <v>66.33969302158197</v>
+        <v>18.93293338587956</v>
       </c>
       <c r="V87" t="n">
-        <v>22.13268755606532</v>
+        <v>1.852669113564409</v>
       </c>
       <c r="AH87" t="n">
-        <v>295.0264294506163</v>
+        <v>583.7100154979884</v>
       </c>
       <c r="AW87" t="n">
-        <v>6.364186166777137</v>
+        <v>4.138415868438337</v>
       </c>
       <c r="DK87" t="n">
-        <v>5.150714891063948</v>
+        <v>2.970732214543739</v>
       </c>
       <c r="DO87" t="n">
-        <v>80.20158721702657</v>
+        <v>26.07027421990441</v>
       </c>
       <c r="EC87" t="n">
-        <v>429.8336028963303</v>
+        <v>352.006568703203</v>
       </c>
       <c r="EF87" t="n">
-        <v>294.5462065361452</v>
+        <v>449.3619356777471</v>
       </c>
       <c r="EO87" t="n">
-        <v>2.241609963998537</v>
+        <v>14.41316487138718</v>
       </c>
       <c r="ER87" t="n">
-        <v>1.421319277480795</v>
+        <v>17.57189233582546</v>
       </c>
       <c r="HL87" t="n">
-        <v>48.75782010108821</v>
+        <v>83.05448884774799</v>
       </c>
       <c r="LA87" t="n">
-        <v>3.663583007240203</v>
+        <v>2.591356733619297</v>
       </c>
     </row>
     <row r="88">
@@ -5680,52 +5943,55 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1479.258840570227</v>
+        <v>2095.492655825975</v>
       </c>
       <c r="G88" t="n">
-        <v>479.860332564211</v>
+        <v>745.8795349030975</v>
+      </c>
+      <c r="J88" t="n">
+        <v>73.14651900756272</v>
       </c>
       <c r="M88" t="n">
-        <v>78.21221065678959</v>
+        <v>44.24902584176772</v>
       </c>
       <c r="P88" t="n">
-        <v>88.6843198108056</v>
+        <v>85.48155824944213</v>
       </c>
       <c r="S88" t="n">
-        <v>70.15152401268708</v>
+        <v>61.87366744664985</v>
       </c>
       <c r="V88" t="n">
-        <v>37.3038985597074</v>
+        <v>37.97620010217373</v>
       </c>
       <c r="AH88" t="n">
-        <v>649.2780848655278</v>
+        <v>332.4183498897968</v>
       </c>
       <c r="AW88" t="n">
-        <v>17.96284864029758</v>
+        <v>9.184761767475585</v>
       </c>
       <c r="DK88" t="n">
-        <v>3.002054415596417</v>
+        <v>9.738119181985624</v>
       </c>
       <c r="DO88" t="n">
-        <v>64.43046161846021</v>
+        <v>88.27180257676905</v>
       </c>
       <c r="EC88" t="n">
-        <v>381.9161866274652</v>
+        <v>684.1712967037041</v>
       </c>
       <c r="EF88" t="n">
-        <v>33.58705567591108</v>
+        <v>474.3704052219344</v>
       </c>
       <c r="EO88" t="n">
-        <v>6.606518894452278</v>
+        <v>13.29096680801969</v>
       </c>
       <c r="ER88" t="n">
-        <v>1.094164716454773</v>
+        <v>6.360513016122729</v>
       </c>
       <c r="HL88" t="n">
-        <v>9.234738712163271</v>
+        <v>51.83885394706661</v>
       </c>
       <c r="LA88" t="n">
-        <v>3.307053019838066</v>
+        <v>3.770062344768814</v>
       </c>
     </row>
     <row r="89">
@@ -5740,52 +6006,55 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2395.585947947776</v>
+        <v>2573.638982992505</v>
       </c>
       <c r="G89" t="n">
-        <v>529.5992780758547</v>
+        <v>421.998374348636</v>
+      </c>
+      <c r="J89" t="n">
+        <v>43.13933942576521</v>
       </c>
       <c r="M89" t="n">
-        <v>10.38130606405028</v>
+        <v>5.649283956929718</v>
       </c>
       <c r="P89" t="n">
-        <v>69.74941109329984</v>
+        <v>0.8946369886341787</v>
       </c>
       <c r="S89" t="n">
-        <v>28.23950011401055</v>
+        <v>47.42148519034078</v>
       </c>
       <c r="V89" t="n">
-        <v>36.861435149272</v>
+        <v>19.75266413621793</v>
       </c>
       <c r="AH89" t="n">
-        <v>143.6211442227296</v>
+        <v>820.8624398387748</v>
       </c>
       <c r="AW89" t="n">
-        <v>5.411949470517365</v>
+        <v>16.38986882421055</v>
       </c>
       <c r="DK89" t="n">
-        <v>3.454846474457771</v>
+        <v>1.803586852437932</v>
       </c>
       <c r="DO89" t="n">
-        <v>8.699414486916712</v>
+        <v>54.41364317395502</v>
       </c>
       <c r="EC89" t="n">
-        <v>876.9123005802596</v>
+        <v>63.93061323028504</v>
       </c>
       <c r="EF89" t="n">
-        <v>161.5639561084927</v>
+        <v>335.576292317968</v>
       </c>
       <c r="EO89" t="n">
-        <v>7.140730507572906</v>
+        <v>11.24964546930799</v>
       </c>
       <c r="ER89" t="n">
-        <v>9.196588439391514</v>
+        <v>10.55155483393888</v>
       </c>
       <c r="HL89" t="n">
-        <v>53.11573425245852</v>
+        <v>37.25626592060301</v>
       </c>
       <c r="LA89" t="n">
-        <v>1.340928638633825</v>
+        <v>3.75227100770582</v>
       </c>
     </row>
     <row r="90">
@@ -5800,52 +6069,55 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>649.9715556832807</v>
+        <v>1133.368039890579</v>
       </c>
       <c r="G90" t="n">
-        <v>339.009794648268</v>
+        <v>710.5672395351783</v>
+      </c>
+      <c r="J90" t="n">
+        <v>51.79029535861508</v>
       </c>
       <c r="M90" t="n">
-        <v>87.42531036025663</v>
+        <v>61.49950574578229</v>
       </c>
       <c r="P90" t="n">
-        <v>15.58384428239424</v>
+        <v>68.85749221141843</v>
       </c>
       <c r="S90" t="n">
-        <v>22.57024338351118</v>
+        <v>46.43176165937219</v>
       </c>
       <c r="V90" t="n">
-        <v>32.84805131525398</v>
+        <v>33.91815259120326</v>
       </c>
       <c r="AH90" t="n">
-        <v>680.8376610703884</v>
+        <v>620.2286555115036</v>
       </c>
       <c r="AW90" t="n">
-        <v>17.98951683397233</v>
+        <v>19.62463654979436</v>
       </c>
       <c r="DK90" t="n">
-        <v>8.360132999958703</v>
+        <v>4.363686154219759</v>
       </c>
       <c r="DO90" t="n">
-        <v>21.9659525162388</v>
+        <v>75.50426474574536</v>
       </c>
       <c r="EC90" t="n">
-        <v>919.2078121640757</v>
+        <v>67.89648166335449</v>
       </c>
       <c r="EF90" t="n">
-        <v>177.5604171205098</v>
+        <v>191.5278111137635</v>
       </c>
       <c r="EO90" t="n">
-        <v>1.410953562416875</v>
+        <v>7.853882184518415</v>
       </c>
       <c r="ER90" t="n">
-        <v>4.866251305611207</v>
+        <v>0.6065144596307226</v>
       </c>
       <c r="HL90" t="n">
-        <v>31.31722268260813</v>
+        <v>32.29540653489216</v>
       </c>
       <c r="LA90" t="n">
-        <v>3.575072739785952</v>
+        <v>3.544526124697168</v>
       </c>
     </row>
     <row r="91">
@@ -5860,52 +6132,55 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2257.489843780506</v>
+        <v>53.09299157564662</v>
       </c>
       <c r="G91" t="n">
-        <v>305.2582992665429</v>
+        <v>736.5700340317824</v>
+      </c>
+      <c r="J91" t="n">
+        <v>98.57379699894254</v>
       </c>
       <c r="M91" t="n">
-        <v>73.04004763708201</v>
+        <v>27.69643698851479</v>
       </c>
       <c r="P91" t="n">
-        <v>24.88444058000042</v>
+        <v>14.20531564750949</v>
       </c>
       <c r="S91" t="n">
-        <v>54.92318601072893</v>
+        <v>17.18997982694291</v>
       </c>
       <c r="V91" t="n">
-        <v>21.79016641379123</v>
+        <v>22.29365260832056</v>
       </c>
       <c r="AH91" t="n">
-        <v>430.0314225542239</v>
+        <v>130.6189724248101</v>
       </c>
       <c r="AW91" t="n">
-        <v>18.5964911412611</v>
+        <v>14.26162191409824</v>
       </c>
       <c r="DK91" t="n">
-        <v>5.288315127253095</v>
+        <v>5.563584364629611</v>
       </c>
       <c r="DO91" t="n">
-        <v>39.08106781525485</v>
+        <v>52.52869766500407</v>
       </c>
       <c r="EC91" t="n">
-        <v>695.3732006386185</v>
+        <v>859.43698269003</v>
       </c>
       <c r="EF91" t="n">
-        <v>174.9894123430883</v>
+        <v>245.9596677882658</v>
       </c>
       <c r="EO91" t="n">
-        <v>5.320068551169741</v>
+        <v>14.84538115241907</v>
       </c>
       <c r="ER91" t="n">
-        <v>10.34381841029424</v>
+        <v>5.695103742756313</v>
       </c>
       <c r="HL91" t="n">
-        <v>92.16279949244196</v>
+        <v>99.6630223744336</v>
       </c>
       <c r="LA91" t="n">
-        <v>3.57243515620254</v>
+        <v>4.720258667132237</v>
       </c>
     </row>
     <row r="92">
@@ -5920,52 +6195,55 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2172.823241697747</v>
+        <v>620.4070839766323</v>
       </c>
       <c r="G92" t="n">
-        <v>537.5335526392821</v>
+        <v>788.3145075461427</v>
+      </c>
+      <c r="J92" t="n">
+        <v>99.35769675334339</v>
       </c>
       <c r="M92" t="n">
-        <v>2.643369457493439</v>
+        <v>31.22553218451625</v>
       </c>
       <c r="P92" t="n">
-        <v>72.44777852047748</v>
+        <v>73.99188128174713</v>
       </c>
       <c r="S92" t="n">
-        <v>21.13034291877505</v>
+        <v>50.22832203357937</v>
       </c>
       <c r="V92" t="n">
-        <v>24.43098720704966</v>
+        <v>7.623329669519774</v>
       </c>
       <c r="AH92" t="n">
-        <v>89.7220909492904</v>
+        <v>359.3609359070741</v>
       </c>
       <c r="AW92" t="n">
-        <v>15.79528003140903</v>
+        <v>4.118156028062716</v>
       </c>
       <c r="DK92" t="n">
-        <v>7.295841183174558</v>
+        <v>9.703085406363366</v>
       </c>
       <c r="DO92" t="n">
-        <v>35.07147990354316</v>
+        <v>99.38391774471937</v>
       </c>
       <c r="EC92" t="n">
-        <v>941.6577761282123</v>
+        <v>418.8993104351239</v>
       </c>
       <c r="EF92" t="n">
-        <v>300.6959513859597</v>
+        <v>2.058917752925271</v>
       </c>
       <c r="EO92" t="n">
-        <v>8.92020548455231</v>
+        <v>2.188571964726365</v>
       </c>
       <c r="ER92" t="n">
-        <v>11.67114658031643</v>
+        <v>5.455498920668136</v>
       </c>
       <c r="HL92" t="n">
-        <v>9.38410493719557</v>
+        <v>79.58989586127352</v>
       </c>
       <c r="LA92" t="n">
-        <v>4.496560143774545</v>
+        <v>0.1317420806221936</v>
       </c>
     </row>
     <row r="93">
@@ -5980,52 +6258,55 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1342.318644061147</v>
+        <v>2496.283490444519</v>
       </c>
       <c r="G93" t="n">
-        <v>94.89442382204621</v>
+        <v>487.2312120211025</v>
+      </c>
+      <c r="J93" t="n">
+        <v>65.63877576326179</v>
       </c>
       <c r="M93" t="n">
-        <v>57.94137834550176</v>
+        <v>85.55319896329343</v>
       </c>
       <c r="P93" t="n">
-        <v>38.89072489816976</v>
+        <v>64.79223062951034</v>
       </c>
       <c r="S93" t="n">
-        <v>50.42654218661961</v>
+        <v>89.49245676990738</v>
       </c>
       <c r="V93" t="n">
-        <v>23.3491594811421</v>
+        <v>29.89038713780331</v>
       </c>
       <c r="AH93" t="n">
-        <v>617.5797671250699</v>
+        <v>144.5441207207154</v>
       </c>
       <c r="AW93" t="n">
-        <v>14.27071608408399</v>
+        <v>10.03410185436943</v>
       </c>
       <c r="DK93" t="n">
-        <v>5.183892315042513</v>
+        <v>3.442786715331521</v>
       </c>
       <c r="DO93" t="n">
-        <v>50.53765582026332</v>
+        <v>57.49623821832839</v>
       </c>
       <c r="EC93" t="n">
-        <v>664.6386389651719</v>
+        <v>613.4602989430659</v>
       </c>
       <c r="EF93" t="n">
-        <v>173.3324004725176</v>
+        <v>294.6399597643107</v>
       </c>
       <c r="EO93" t="n">
-        <v>2.396546303396034</v>
+        <v>6.165225066330848</v>
       </c>
       <c r="ER93" t="n">
-        <v>12.67687848561573</v>
+        <v>8.49885135118827</v>
       </c>
       <c r="HL93" t="n">
-        <v>24.03451610657562</v>
+        <v>47.90490955582128</v>
       </c>
       <c r="LA93" t="n">
-        <v>3.871999702947881</v>
+        <v>4.623152126426101</v>
       </c>
     </row>
     <row r="94">
@@ -6040,52 +6321,55 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2502.444929287494</v>
+        <v>1103.554614800732</v>
       </c>
       <c r="G94" t="n">
-        <v>162.57321800011</v>
+        <v>591.1205911668014</v>
+      </c>
+      <c r="J94" t="n">
+        <v>21.73044898822895</v>
       </c>
       <c r="M94" t="n">
-        <v>62.31045705397031</v>
+        <v>25.05350323464085</v>
       </c>
       <c r="P94" t="n">
-        <v>65.42877798909997</v>
+        <v>27.80466252151725</v>
       </c>
       <c r="S94" t="n">
-        <v>76.31425076680351</v>
+        <v>7.419444465684344</v>
       </c>
       <c r="V94" t="n">
-        <v>0.4693506923013957</v>
+        <v>37.05482273685118</v>
       </c>
       <c r="AH94" t="n">
-        <v>844.0298051952553</v>
+        <v>252.8628585660714</v>
       </c>
       <c r="AW94" t="n">
-        <v>10.37929975267033</v>
+        <v>5.546129471172137</v>
       </c>
       <c r="DK94" t="n">
-        <v>3.172642745378083</v>
+        <v>4.170788162050256</v>
       </c>
       <c r="DO94" t="n">
-        <v>19.00259555803651</v>
+        <v>24.01114137022076</v>
       </c>
       <c r="EC94" t="n">
-        <v>876.6420601151744</v>
+        <v>874.7891935773383</v>
       </c>
       <c r="EF94" t="n">
-        <v>139.0310139696115</v>
+        <v>4.171520647730464</v>
       </c>
       <c r="EO94" t="n">
-        <v>2.491559807727934</v>
+        <v>14.76144879727672</v>
       </c>
       <c r="ER94" t="n">
-        <v>11.77935187315374</v>
+        <v>6.473236546796102</v>
       </c>
       <c r="HL94" t="n">
-        <v>83.02684724031562</v>
+        <v>40.02670781933752</v>
       </c>
       <c r="LA94" t="n">
-        <v>4.082544971313029</v>
+        <v>2.173073806926378</v>
       </c>
     </row>
     <row r="95">
@@ -6100,52 +6384,55 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1143.17100811752</v>
+        <v>1436.656470131779</v>
       </c>
       <c r="G95" t="n">
-        <v>327.1111005644654</v>
+        <v>583.8818200012256</v>
+      </c>
+      <c r="J95" t="n">
+        <v>66.01253386734544</v>
       </c>
       <c r="M95" t="n">
-        <v>1.455958235048715</v>
+        <v>20.34531410856935</v>
       </c>
       <c r="P95" t="n">
-        <v>47.568037937797</v>
+        <v>15.3708597343022</v>
       </c>
       <c r="S95" t="n">
-        <v>12.57815245108835</v>
+        <v>68.30090538421038</v>
       </c>
       <c r="V95" t="n">
-        <v>13.21861812834092</v>
+        <v>43.40918075365329</v>
       </c>
       <c r="AH95" t="n">
-        <v>586.3573897619374</v>
+        <v>433.4846181121206</v>
       </c>
       <c r="AW95" t="n">
-        <v>5.282799892277541</v>
+        <v>16.43878331955844</v>
       </c>
       <c r="DK95" t="n">
-        <v>3.080674987287648</v>
+        <v>4.117409426412778</v>
       </c>
       <c r="DO95" t="n">
-        <v>93.2637024260363</v>
+        <v>97.55866183540934</v>
       </c>
       <c r="EC95" t="n">
-        <v>831.4596564213612</v>
+        <v>568.4868191258917</v>
       </c>
       <c r="EF95" t="n">
-        <v>119.7991045120135</v>
+        <v>93.30338060081311</v>
       </c>
       <c r="EO95" t="n">
-        <v>11.64146973021978</v>
+        <v>13.75299489986103</v>
       </c>
       <c r="ER95" t="n">
-        <v>18.96478359566553</v>
+        <v>12.90305873042031</v>
       </c>
       <c r="HL95" t="n">
-        <v>41.52825320609877</v>
+        <v>32.96510179419138</v>
       </c>
       <c r="LA95" t="n">
-        <v>1.389325091353244</v>
+        <v>1.889180464402711</v>
       </c>
     </row>
     <row r="96">
@@ -6160,52 +6447,55 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1506.03080542201</v>
+        <v>722.6964177351539</v>
       </c>
       <c r="G96" t="n">
-        <v>69.25307642718535</v>
+        <v>622.4891732458846</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5.182032922672186</v>
       </c>
       <c r="M96" t="n">
-        <v>5.610464520158409</v>
+        <v>11.27303585346924</v>
       </c>
       <c r="P96" t="n">
-        <v>12.5611343007711</v>
+        <v>36.09274698800197</v>
       </c>
       <c r="S96" t="n">
-        <v>1.520058859600526</v>
+        <v>65.50817808544961</v>
       </c>
       <c r="V96" t="n">
-        <v>9.731275927167138</v>
+        <v>24.10822499577391</v>
       </c>
       <c r="AH96" t="n">
-        <v>495.151421007459</v>
+        <v>922.0524002205615</v>
       </c>
       <c r="AW96" t="n">
-        <v>2.073807209059608</v>
+        <v>15.60563793672635</v>
       </c>
       <c r="DK96" t="n">
-        <v>5.528508424393859</v>
+        <v>9.098369500581111</v>
       </c>
       <c r="DO96" t="n">
-        <v>98.42699319022383</v>
+        <v>13.09730391044743</v>
       </c>
       <c r="EC96" t="n">
-        <v>21.45468176340282</v>
+        <v>776.4237427599726</v>
       </c>
       <c r="EF96" t="n">
-        <v>158.2741721264939</v>
+        <v>414.3868690351008</v>
       </c>
       <c r="EO96" t="n">
-        <v>2.799996380322722</v>
+        <v>7.07278991467075</v>
       </c>
       <c r="ER96" t="n">
-        <v>1.256341480234864</v>
+        <v>12.72888689091214</v>
       </c>
       <c r="HL96" t="n">
-        <v>95.6637089125292</v>
+        <v>39.8126290983958</v>
       </c>
       <c r="LA96" t="n">
-        <v>2.880086937314059</v>
+        <v>3.746651277777877</v>
       </c>
     </row>
     <row r="97">
@@ -6220,52 +6510,55 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>398.8234326897116</v>
+        <v>1709.748001767953</v>
       </c>
       <c r="G97" t="n">
-        <v>21.26494904980527</v>
+        <v>472.1484974974931</v>
+      </c>
+      <c r="J97" t="n">
+        <v>96.52348502414493</v>
       </c>
       <c r="M97" t="n">
-        <v>7.124376102797047</v>
+        <v>70.96350039905914</v>
       </c>
       <c r="P97" t="n">
-        <v>66.19059907875815</v>
+        <v>44.61950054515714</v>
       </c>
       <c r="S97" t="n">
-        <v>61.05410873111123</v>
+        <v>58.2367233304835</v>
       </c>
       <c r="V97" t="n">
-        <v>24.62183255033024</v>
+        <v>42.49617950195782</v>
       </c>
       <c r="AH97" t="n">
-        <v>149.2206898636943</v>
+        <v>476.0646817267691</v>
       </c>
       <c r="AW97" t="n">
-        <v>8.333052620398195</v>
+        <v>16.11652369741927</v>
       </c>
       <c r="DK97" t="n">
-        <v>0.1411899586829202</v>
+        <v>6.372722769916077</v>
       </c>
       <c r="DO97" t="n">
-        <v>64.85860369142291</v>
+        <v>35.70765388036041</v>
       </c>
       <c r="EC97" t="n">
-        <v>125.9849816858172</v>
+        <v>944.6561534259656</v>
       </c>
       <c r="EF97" t="n">
-        <v>141.4024524977749</v>
+        <v>312.1781276351629</v>
       </c>
       <c r="EO97" t="n">
-        <v>2.676379678977752</v>
+        <v>10.10953686531501</v>
       </c>
       <c r="ER97" t="n">
-        <v>18.02053373866676</v>
+        <v>4.364236262395849</v>
       </c>
       <c r="HL97" t="n">
-        <v>82.69622772059533</v>
+        <v>26.19338920241249</v>
       </c>
       <c r="LA97" t="n">
-        <v>3.465928147931495</v>
+        <v>1.965510900392865</v>
       </c>
     </row>
     <row r="98">
@@ -6280,52 +6573,55 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2573.699082564214</v>
+        <v>1414.594351520882</v>
       </c>
       <c r="G98" t="n">
-        <v>312.0682504950259</v>
+        <v>554.1334536872899</v>
+      </c>
+      <c r="J98" t="n">
+        <v>54.33024993026273</v>
       </c>
       <c r="M98" t="n">
-        <v>4.832761927703877</v>
+        <v>16.71525418057216</v>
       </c>
       <c r="P98" t="n">
-        <v>38.37084468799684</v>
+        <v>42.50108779247109</v>
       </c>
       <c r="S98" t="n">
-        <v>23.49992147596818</v>
+        <v>78.77287071436876</v>
       </c>
       <c r="V98" t="n">
-        <v>42.94216525256768</v>
+        <v>19.32820939530462</v>
       </c>
       <c r="AH98" t="n">
-        <v>184.3536963254195</v>
+        <v>656.1477495158745</v>
       </c>
       <c r="AW98" t="n">
-        <v>1.840461307543333</v>
+        <v>7.32956822733647</v>
       </c>
       <c r="DK98" t="n">
-        <v>3.71179980265265</v>
+        <v>3.084924879596314</v>
       </c>
       <c r="DO98" t="n">
-        <v>55.58832078598498</v>
+        <v>5.685186452726187</v>
       </c>
       <c r="EC98" t="n">
-        <v>734.2549657278646</v>
+        <v>194.6794436983159</v>
       </c>
       <c r="EF98" t="n">
-        <v>465.836794881925</v>
+        <v>450.6800824632975</v>
       </c>
       <c r="EO98" t="n">
-        <v>17.72051931828191</v>
+        <v>19.34917522196172</v>
       </c>
       <c r="ER98" t="n">
-        <v>14.78417461410066</v>
+        <v>0.7318137339367237</v>
       </c>
       <c r="HL98" t="n">
-        <v>68.76962899194496</v>
+        <v>90.3773979426398</v>
       </c>
       <c r="LA98" t="n">
-        <v>4.418063799987077</v>
+        <v>0.7467205465204391</v>
       </c>
     </row>
     <row r="99">
@@ -6340,52 +6636,55 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2483.33333239076</v>
+        <v>1854.552489407808</v>
       </c>
       <c r="G99" t="n">
-        <v>170.3609993099407</v>
+        <v>508.1440901008471</v>
+      </c>
+      <c r="J99" t="n">
+        <v>91.40110613800456</v>
       </c>
       <c r="M99" t="n">
-        <v>31.73986052744748</v>
+        <v>71.49648339293286</v>
       </c>
       <c r="P99" t="n">
-        <v>11.15865262998422</v>
+        <v>1.575301753166092</v>
       </c>
       <c r="S99" t="n">
-        <v>2.557486566911704</v>
+        <v>48.55453991749044</v>
       </c>
       <c r="V99" t="n">
-        <v>4.409606506755376</v>
+        <v>18.30728686309132</v>
       </c>
       <c r="AH99" t="n">
-        <v>951.8763918622764</v>
+        <v>728.8857948424882</v>
       </c>
       <c r="AW99" t="n">
-        <v>7.691511584114103</v>
+        <v>3.882723809289939</v>
       </c>
       <c r="DK99" t="n">
-        <v>0.4779677098809509</v>
+        <v>9.555614735247959</v>
       </c>
       <c r="DO99" t="n">
-        <v>2.494460250514607</v>
+        <v>41.40537872424503</v>
       </c>
       <c r="EC99" t="n">
-        <v>220.0172450809488</v>
+        <v>684.6585438431559</v>
       </c>
       <c r="EF99" t="n">
-        <v>184.6033446068737</v>
+        <v>320.8835574068128</v>
       </c>
       <c r="EO99" t="n">
-        <v>12.07765351969348</v>
+        <v>0.09743896964144572</v>
       </c>
       <c r="ER99" t="n">
-        <v>2.239868018203872</v>
+        <v>5.277375934068931</v>
       </c>
       <c r="HL99" t="n">
-        <v>13.98150619104991</v>
+        <v>52.27666518060276</v>
       </c>
       <c r="LA99" t="n">
-        <v>2.600958572011751</v>
+        <v>4.265819410387595</v>
       </c>
     </row>
     <row r="100">
@@ -6400,52 +6699,55 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2910.269039570536</v>
+        <v>2408.17182726795</v>
       </c>
       <c r="G100" t="n">
-        <v>741.3302794660414</v>
+        <v>43.3764322266164</v>
+      </c>
+      <c r="J100" t="n">
+        <v>26.10166552532358</v>
       </c>
       <c r="M100" t="n">
-        <v>12.23895396448198</v>
+        <v>37.37548750891501</v>
       </c>
       <c r="P100" t="n">
-        <v>25.28696479883907</v>
+        <v>19.75946674269968</v>
       </c>
       <c r="S100" t="n">
-        <v>36.2905898697724</v>
+        <v>46.98665698635232</v>
       </c>
       <c r="V100" t="n">
-        <v>25.1668863200469</v>
+        <v>3.326174859294423</v>
       </c>
       <c r="AH100" t="n">
-        <v>268.2633390589731</v>
+        <v>911.7594562954911</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.3411623473356551</v>
+        <v>7.150113448193894</v>
       </c>
       <c r="DK100" t="n">
-        <v>2.660625821169356</v>
+        <v>1.713493200730692</v>
       </c>
       <c r="DO100" t="n">
-        <v>48.13380125290919</v>
+        <v>27.54863135079919</v>
       </c>
       <c r="EC100" t="n">
-        <v>123.6678478305913</v>
+        <v>320.4249308230052</v>
       </c>
       <c r="EF100" t="n">
-        <v>333.2826707318582</v>
+        <v>231.3586844341848</v>
       </c>
       <c r="EO100" t="n">
-        <v>4.04489194664796</v>
+        <v>19.32360779071323</v>
       </c>
       <c r="ER100" t="n">
-        <v>18.80863779475353</v>
+        <v>13.90133118268158</v>
       </c>
       <c r="HL100" t="n">
-        <v>19.6021352939901</v>
+        <v>32.46990753855781</v>
       </c>
       <c r="LA100" t="n">
-        <v>0.9232891595320819</v>
+        <v>2.951022057621566</v>
       </c>
     </row>
     <row r="101">
@@ -6460,52 +6762,55 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2838.559715184556</v>
+        <v>1761.352577903446</v>
       </c>
       <c r="G101" t="n">
-        <v>705.8538667543015</v>
+        <v>388.8644326121058</v>
+      </c>
+      <c r="J101" t="n">
+        <v>63.13127511344157</v>
       </c>
       <c r="M101" t="n">
-        <v>73.1324136830489</v>
+        <v>57.30913364971714</v>
       </c>
       <c r="P101" t="n">
-        <v>83.74136554330092</v>
+        <v>10.62902224325859</v>
       </c>
       <c r="S101" t="n">
-        <v>80.70572792587699</v>
+        <v>77.99011130842092</v>
       </c>
       <c r="V101" t="n">
-        <v>42.52094481450288</v>
+        <v>34.72781177459917</v>
       </c>
       <c r="AH101" t="n">
-        <v>880.661312649907</v>
+        <v>439.1633901723284</v>
       </c>
       <c r="AW101" t="n">
-        <v>2.37855368111171</v>
+        <v>3.66082148522741</v>
       </c>
       <c r="DK101" t="n">
-        <v>6.416727791108451</v>
+        <v>9.705666874137142</v>
       </c>
       <c r="DO101" t="n">
-        <v>42.37631993245886</v>
+        <v>43.19001525155655</v>
       </c>
       <c r="EC101" t="n">
-        <v>70.92070699753161</v>
+        <v>336.9373849284116</v>
       </c>
       <c r="EF101" t="n">
-        <v>377.8682459980741</v>
+        <v>237.8593759039327</v>
       </c>
       <c r="EO101" t="n">
-        <v>18.11824932450303</v>
+        <v>5.263091180119646</v>
       </c>
       <c r="ER101" t="n">
-        <v>5.71811157452395</v>
+        <v>7.691920353126744</v>
       </c>
       <c r="HL101" t="n">
-        <v>82.01296343799908</v>
+        <v>16.64379831215314</v>
       </c>
       <c r="LA101" t="n">
-        <v>2.387111628628485</v>
+        <v>0.9571454126059475</v>
       </c>
     </row>
   </sheetData>
